--- a/downloads/apartment-sales-tracker.xlsx
+++ b/downloads/apartment-sales-tracker.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q313"/>
+  <dimension ref="A1:Q311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -740,192 +740,318 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="7" t="n"/>
     </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>דירות בפרויקט</t>
+        </is>
+      </c>
+      <c r="C5" s="9">
+        <f>COUNTA($C$12:$C$311)</f>
+        <v>6</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>שווי מכירות (חוזים) (₪)</t>
+        </is>
+      </c>
+      <c r="G5" s="10">
+        <f>SUMPRODUCT((($H$12:$H$311="נחתם חוזה")+($H$12:$H$311="נמסרה"))*($G$12:$G$311))</f>
+        <v>8540000</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>דירות בפרויקט</t>
+          <t>נמכרו (חוזה / נמסרו)</t>
         </is>
       </c>
       <c r="C6" s="9">
-        <f>COUNTA($C$14:$C$313)</f>
-        <v>6</v>
+        <f>COUNTIF($H$12:$H$311,"נחתם חוזה")+COUNTIF($H$12:$H$311,"נמסרה")</f>
+        <v>3</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>שווי מכירות (חוזים) (₪)</t>
+          <t>נגבה מהרוכשים (₪)</t>
         </is>
       </c>
       <c r="G6" s="10">
-        <f>SUMPRODUCT((($H$14:$H$313="נחתם חוזה")+($H$14:$H$313="נמסרה"))*($G$14:$G$313))</f>
-        <v>8540000</v>
+        <f>SUM($K$12:$K$311)</f>
+        <v>4828000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>נמכרו (חוזה / נמסרו)</t>
+          <t>שמורות / במו״מ</t>
         </is>
       </c>
       <c r="C7" s="9">
-        <f>COUNTIF($H$14:$H$313,"נחתם חוזה")+COUNTIF($H$14:$H$313,"נמסרה")</f>
-        <v>3</v>
+        <f>COUNTIF($H$12:$H$311,"שמורה / במו״מ")</f>
+        <v>1</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>נגבה מהרוכשים (₪)</t>
+          <t>נשאר לגבות (₪)</t>
         </is>
       </c>
       <c r="G7" s="10">
-        <f>SUM($K$14:$K$313)</f>
-        <v>4828000</v>
+        <f>G5-G6</f>
+        <v>3712000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>שמורות / במו״מ</t>
+          <t>פנויות</t>
         </is>
       </c>
       <c r="C8" s="9">
-        <f>COUNTIF($H$14:$H$313,"שמורה / במו״מ")</f>
-        <v>1</v>
+        <f>COUNTIF($H$12:$H$311,"פנויה")</f>
+        <v>2</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>נשאר לגבות (₪)</t>
+          <t>מלאי פנוי לפי מחירון (₪)</t>
         </is>
       </c>
       <c r="G8" s="10">
-        <f>G6-G7</f>
-        <v>3712000</v>
+        <f>SUMPRODUCT(($H$12:$H$311&lt;&gt;"נחתם חוזה")*($H$12:$H$311&lt;&gt;"נמסרה")*($C$12:$C$311&lt;&gt;"")*($F$12:$F$311))</f>
+        <v>6760000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>פנויות</t>
-        </is>
-      </c>
-      <c r="C9" s="9">
-        <f>COUNTIF($H$14:$H$313,"פנויה")</f>
-        <v>2</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>מלאי פנוי לפי מחירון (₪)</t>
-        </is>
-      </c>
-      <c r="G9" s="10">
-        <f>SUMPRODUCT(($H$14:$H$313&lt;&gt;"נחתם חוזה")*($H$14:$H$313&lt;&gt;"נמסרה")*($C$14:$C$313&lt;&gt;"")*($F$14:$F$313))</f>
-        <v>6760000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
           <t>אחוז מכירות</t>
         </is>
       </c>
-      <c r="C10" s="11">
-        <f>IFERROR(C7/C6,0)</f>
+      <c r="C9" s="11">
+        <f>IFERROR(C6/C5,0)</f>
         <v>0.5</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>מחיר ממוצע למ״ר (נמכרו) (₪)</t>
         </is>
       </c>
-      <c r="G10" s="10">
-        <f>IFERROR(SUMPRODUCT((($H$14:$H$313="נחתם חוזה")+($H$14:$H$313="נמסרה"))*($G$14:$G$313))/SUMPRODUCT((($H$14:$H$313="נחתם חוזה")+($H$14:$H$313="נמסרה"))*($E$14:$E$313)),0)</f>
+      <c r="G9" s="10">
+        <f>IFERROR(SUMPRODUCT((($H$12:$H$311="נחתם חוזה")+($H$12:$H$311="נמסרה"))*($G$12:$G$311))/SUMPRODUCT((($H$12:$H$311="נחתם חוזה")+($H$12:$H$311="נמסרה"))*($E$12:$E$311)),0)</f>
         <v>22895.4423592493</v>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>בניין</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>קומה</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>מס׳ דירה</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>חדרים</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>שטח (מ״ר)</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>מחיר מחירון (₪)</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>מחיר סופי (₪)</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>סטטוס</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>רוכש/ת</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>טלפון</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>שולם (₪)</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>יתרה (₪)</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>אחוז ששולם</t>
         </is>
       </c>
-      <c r="N13" s="12" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>מחיר למ״ר (₪)</t>
         </is>
       </c>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
         <is>
           <t>תאריך חוזה</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>חניה / מחסן</t>
         </is>
       </c>
-      <c r="Q13" s="12" t="inlineStr">
+      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>בניין A</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>105</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>2290000</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>נחתם חוזה</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>משפחת כהן</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>050-0000000</t>
+        </is>
+      </c>
+      <c r="K12" s="18">
+        <f>IF(C12="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C12,'תשלומי רוכשים'!$F$8:$F$507))</f>
+        <v>858000</v>
+      </c>
+      <c r="L12" s="18">
+        <f>IF(OR(C12="",AND(H12&lt;&gt;"נחתם חוזה",H12&lt;&gt;"נמסרה")),"",IF(G12="",F12,G12)-N(K12))</f>
+        <v>1432000</v>
+      </c>
+      <c r="M12" s="19">
+        <f>IF(L12="","",IFERROR(N(K12)/IF(G12="",F12,G12),0))</f>
+        <v>0.374672489082969</v>
+      </c>
+      <c r="N12" s="18">
+        <f>IF(OR(C12="",N(E12)=0),"",IF(G12="",F12,G12)/E12)</f>
+        <v>21809.5238095238</v>
+      </c>
+      <c r="O12" s="20" t="n">
+        <v>46109</v>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>חניה 12, מחסן 3</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>בניין A</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>שמורה / במו״מ</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>דנה לוי</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>052-0000000</t>
+        </is>
+      </c>
+      <c r="K13" s="18">
+        <f>IF(C13="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C13,'תשלומי רוכשים'!$F$8:$F$507))</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="18" t="str">
+        <f>IF(OR(C13="",AND(H13&lt;&gt;"נחתם חוזה",H13&lt;&gt;"נמסרה")),"",IF(G13="",F13,G13)-N(K13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="19" t="str">
+        <f>IF(L13="","",IFERROR(N(K13)/IF(G13="",F13,G13),0))</f>
+        <v/>
+      </c>
+      <c r="N13" s="18">
+        <f>IF(OR(C13="",N(E13)=0),"",IF(G13="",F13,G13)/E13)</f>
+        <v>22941.1764705882</v>
+      </c>
+      <c r="O13" s="20" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -934,24 +1060,24 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>A-1</t>
+          <t>A-3</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>2350000</v>
+        <v>2890000</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>2290000</v>
+        <v>2850000</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -960,36 +1086,36 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>משפחת כהן</t>
+          <t>יוסי ומיכל אברהם</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>050-0000000</t>
+          <t>054-0000000</t>
         </is>
       </c>
       <c r="K14" s="18">
         <f>IF(C14="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C14,'תשלומי רוכשים'!$F$8:$F$507))</f>
-        <v>858000</v>
+        <v>570000</v>
       </c>
       <c r="L14" s="18">
         <f>IF(OR(C14="",AND(H14&lt;&gt;"נחתם חוזה",H14&lt;&gt;"נמסרה")),"",IF(G14="",F14,G14)-N(K14))</f>
-        <v>1432000</v>
+        <v>2280000</v>
       </c>
       <c r="M14" s="19">
         <f>IF(L14="","",IFERROR(N(K14)/IF(G14="",F14,G14),0))</f>
-        <v>0.374672489082969</v>
+        <v>0.2</v>
       </c>
       <c r="N14" s="18">
         <f>IF(OR(C14="",N(E14)=0),"",IF(G14="",F14,G14)/E14)</f>
-        <v>21809.5238095238</v>
+        <v>22265.625</v>
       </c>
       <c r="O14" s="20" t="n">
-        <v>46109</v>
+        <v>46189</v>
       </c>
       <c r="P14" s="5" t="inlineStr">
         <is>
-          <t>חניה 12, מחסן 3</t>
+          <t>2 חניות</t>
         </is>
       </c>
       <c r="Q14" s="5" t="n"/>
@@ -1001,38 +1127,30 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>A-2</t>
+          <t>A-4</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>1950000</v>
+        <v>2390000</v>
       </c>
       <c r="G15" s="21" t="n"/>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>שמורה / במו״מ</t>
+          <t>פנויה</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>דנה לוי</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>052-0000000</t>
-        </is>
-      </c>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="14" t="n"/>
       <c r="K15" s="18">
         <f>IF(C15="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C15,'תשלומי רוכשים'!$F$8:$F$507))</f>
         <v>0</v>
@@ -1047,7 +1165,7 @@
       </c>
       <c r="N15" s="18">
         <f>IF(OR(C15="",N(E15)=0),"",IF(G15="",F15,G15)/E15)</f>
-        <v>22941.1764705882</v>
+        <v>22980.7692307692</v>
       </c>
       <c r="O15" s="20" t="n"/>
       <c r="P15" s="5" t="n"/>
@@ -1060,64 +1178,48 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>A-3</t>
+          <t>A-5</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>2890000</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>2850000</v>
-      </c>
+        <v>2420000</v>
+      </c>
+      <c r="G16" s="21" t="n"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>נחתם חוזה</t>
+          <t>פנויה</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>יוסי ומיכל אברהם</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>054-0000000</t>
-        </is>
-      </c>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="14" t="n"/>
       <c r="K16" s="18">
         <f>IF(C16="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C16,'תשלומי רוכשים'!$F$8:$F$507))</f>
-        <v>570000</v>
-      </c>
-      <c r="L16" s="18">
+        <v>0</v>
+      </c>
+      <c r="L16" s="18" t="str">
         <f>IF(OR(C16="",AND(H16&lt;&gt;"נחתם חוזה",H16&lt;&gt;"נמסרה")),"",IF(G16="",F16,G16)-N(K16))</f>
-        <v>2280000</v>
-      </c>
-      <c r="M16" s="19">
+        <v/>
+      </c>
+      <c r="M16" s="19" t="str">
         <f>IF(L16="","",IFERROR(N(K16)/IF(G16="",F16,G16),0))</f>
-        <v>0.2</v>
+        <v/>
       </c>
       <c r="N16" s="18">
         <f>IF(OR(C16="",N(E16)=0),"",IF(G16="",F16,G16)/E16)</f>
-        <v>22265.625</v>
-      </c>
-      <c r="O16" s="20" t="n">
-        <v>46189</v>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>2 חניות</t>
-        </is>
-      </c>
+        <v>23269.2307692308</v>
+      </c>
+      <c r="O16" s="20" t="n"/>
+      <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
     </row>
     <row r="17">
@@ -1127,84 +1229,80 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>A-4</t>
+          <t>A-6</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>2390000</v>
-      </c>
-      <c r="G17" s="21" t="n"/>
+        <v>3450000</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>3400000</v>
+      </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>פנויה</t>
+          <t>נמסרה</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="14" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>רון גולן</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>053-0000000</t>
+        </is>
+      </c>
       <c r="K17" s="18">
         <f>IF(C17="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C17,'תשלומי רוכשים'!$F$8:$F$507))</f>
+        <v>3400000</v>
+      </c>
+      <c r="L17" s="18">
+        <f>IF(OR(C17="",AND(H17&lt;&gt;"נחתם חוזה",H17&lt;&gt;"נמסרה")),"",IF(G17="",F17,G17)-N(K17))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="18" t="str">
-        <f>IF(OR(C17="",AND(H17&lt;&gt;"נחתם חוזה",H17&lt;&gt;"נמסרה")),"",IF(G17="",F17,G17)-N(K17))</f>
-        <v/>
-      </c>
-      <c r="M17" s="19" t="str">
+      <c r="M17" s="19">
         <f>IF(L17="","",IFERROR(N(K17)/IF(G17="",F17,G17),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N17" s="18">
         <f>IF(OR(C17="",N(E17)=0),"",IF(G17="",F17,G17)/E17)</f>
-        <v>22980.7692307692</v>
-      </c>
-      <c r="O17" s="20" t="n"/>
-      <c r="P17" s="5" t="n"/>
+        <v>24285.7142857143</v>
+      </c>
+      <c r="O17" s="20" t="n">
+        <v>45609</v>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>חניה 1</t>
+        </is>
+      </c>
       <c r="Q17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>בניין A</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>A-5</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>104</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>2420000</v>
-      </c>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="21" t="n"/>
       <c r="G18" s="21" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>פנויה</t>
-        </is>
-      </c>
+      <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="14" t="n"/>
-      <c r="K18" s="18">
+      <c r="K18" s="18" t="str">
         <f>IF(C18="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C18,'תשלומי רוכשים'!$F$8:$F$507))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="L18" s="18" t="str">
         <f>IF(OR(C18="",AND(H18&lt;&gt;"נחתם חוזה",H18&lt;&gt;"נמסרה")),"",IF(G18="",F18,G18)-N(K18))</f>
@@ -1214,79 +1312,43 @@
         <f>IF(L18="","",IFERROR(N(K18)/IF(G18="",F18,G18),0))</f>
         <v/>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="18" t="str">
         <f>IF(OR(C18="",N(E18)=0),"",IF(G18="",F18,G18)/E18)</f>
-        <v>23269.2307692308</v>
+        <v/>
       </c>
       <c r="O18" s="20" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>בניין A</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>A-6</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="F19" s="17" t="n">
-        <v>3450000</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>נמסרה</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>רון גולן</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
-        <is>
-          <t>053-0000000</t>
-        </is>
-      </c>
-      <c r="K19" s="18">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="18" t="str">
         <f>IF(C19="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C19,'תשלומי רוכשים'!$F$8:$F$507))</f>
-        <v>3400000</v>
-      </c>
-      <c r="L19" s="18">
+        <v/>
+      </c>
+      <c r="L19" s="18" t="str">
         <f>IF(OR(C19="",AND(H19&lt;&gt;"נחתם חוזה",H19&lt;&gt;"נמסרה")),"",IF(G19="",F19,G19)-N(K19))</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="19">
+        <v/>
+      </c>
+      <c r="M19" s="19" t="str">
         <f>IF(L19="","",IFERROR(N(K19)/IF(G19="",F19,G19),0))</f>
-        <v>1</v>
-      </c>
-      <c r="N19" s="18">
+        <v/>
+      </c>
+      <c r="N19" s="18" t="str">
         <f>IF(OR(C19="",N(E19)=0),"",IF(G19="",F19,G19)/E19)</f>
-        <v>24285.7142857143</v>
-      </c>
-      <c r="O19" s="20" t="n">
-        <v>45609</v>
-      </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>חניה 1</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="O19" s="20" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
     </row>
     <row r="20">
@@ -10341,89 +10403,27 @@
       <c r="P311" s="5" t="n"/>
       <c r="Q311" s="5" t="n"/>
     </row>
-    <row r="312">
-      <c r="A312" s="5" t="n"/>
-      <c r="B312" s="13" t="n"/>
-      <c r="C312" s="14" t="n"/>
-      <c r="D312" s="15" t="n"/>
-      <c r="E312" s="22" t="n"/>
-      <c r="F312" s="21" t="n"/>
-      <c r="G312" s="21" t="n"/>
-      <c r="H312" s="5" t="n"/>
-      <c r="I312" s="5" t="n"/>
-      <c r="J312" s="14" t="n"/>
-      <c r="K312" s="18" t="str">
-        <f>IF(C312="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C312,'תשלומי רוכשים'!$F$8:$F$507))</f>
-        <v/>
-      </c>
-      <c r="L312" s="18" t="str">
-        <f>IF(OR(C312="",AND(H312&lt;&gt;"נחתם חוזה",H312&lt;&gt;"נמסרה")),"",IF(G312="",F312,G312)-N(K312))</f>
-        <v/>
-      </c>
-      <c r="M312" s="19" t="str">
-        <f>IF(L312="","",IFERROR(N(K312)/IF(G312="",F312,G312),0))</f>
-        <v/>
-      </c>
-      <c r="N312" s="18" t="str">
-        <f>IF(OR(C312="",N(E312)=0),"",IF(G312="",F312,G312)/E312)</f>
-        <v/>
-      </c>
-      <c r="O312" s="20" t="n"/>
-      <c r="P312" s="5" t="n"/>
-      <c r="Q312" s="5" t="n"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="5" t="n"/>
-      <c r="B313" s="13" t="n"/>
-      <c r="C313" s="14" t="n"/>
-      <c r="D313" s="15" t="n"/>
-      <c r="E313" s="22" t="n"/>
-      <c r="F313" s="21" t="n"/>
-      <c r="G313" s="21" t="n"/>
-      <c r="H313" s="5" t="n"/>
-      <c r="I313" s="5" t="n"/>
-      <c r="J313" s="14" t="n"/>
-      <c r="K313" s="18" t="str">
-        <f>IF(C313="","",SUMIF('תשלומי רוכשים'!$A$8:$A$507,C313,'תשלומי רוכשים'!$F$8:$F$507))</f>
-        <v/>
-      </c>
-      <c r="L313" s="18" t="str">
-        <f>IF(OR(C313="",AND(H313&lt;&gt;"נחתם חוזה",H313&lt;&gt;"נמסרה")),"",IF(G313="",F313,G313)-N(K313))</f>
-        <v/>
-      </c>
-      <c r="M313" s="19" t="str">
-        <f>IF(L313="","",IFERROR(N(K313)/IF(G313="",F313,G313),0))</f>
-        <v/>
-      </c>
-      <c r="N313" s="18" t="str">
-        <f>IF(OR(C313="",N(E313)=0),"",IF(G313="",F313,G313)/E313)</f>
-        <v/>
-      </c>
-      <c r="O313" s="20" t="n"/>
-      <c r="P313" s="5" t="n"/>
-      <c r="Q313" s="5" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B4:D4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H14:H313">
+  <conditionalFormatting sqref="H12:H311">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>H14="פנויה"</formula>
+      <formula>H12="פנויה"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>H14="שמורה / במו״מ"</formula>
+      <formula>H12="שמורה / במו״מ"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>H14="נחתם חוזה"</formula>
+      <formula>H12="נחתם חוזה"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H14="נמסרה"</formula>
+      <formula>H12="נמסרה"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M14:M313">
+  <conditionalFormatting sqref="M12:M311">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -10433,10 +10433,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H14:H313" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא ברשימה" error="יש לבחור מהרשימה (אפשר לערוך אותה בגיליון הרשימות)" type="list" errorStyle="warning">
+    <dataValidation sqref="H12:H311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא ברשימה" error="יש לבחור מהרשימה (אפשר לערוך אותה בגיליון הרשימות)" type="list" errorStyle="warning">
       <formula1>=AptStatus</formula1>
     </dataValidation>
-    <dataValidation sqref="E14:G313" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="יש להזין מספר" type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+    <dataValidation sqref="E12:G311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="יש להזין מספר" type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="str">
-        <f>IF(A8="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A8,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A8="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A8,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v>משפחת כהן</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="B9" s="23" t="str">
-        <f>IF(A9="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A9,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A9="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A9,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v>משפחת כהן</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="B10" s="23" t="str">
-        <f>IF(A10="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A10,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A10="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A10,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v>משפחת כהן</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="B11" s="23" t="str">
-        <f>IF(A11="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A11,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A11="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A11,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v>יוסי ומיכל אברהם</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B12" s="23" t="str">
-        <f>IF(A12="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A12,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A12="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A12,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v>יוסי ומיכל אברהם</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="B13" s="23" t="str">
-        <f>IF(A13="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A13,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A13="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A13,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v>רון גולן</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -10768,7 +10768,7 @@
     <row r="14">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="23" t="str">
-        <f>IF(A14="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A14,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A14="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A14,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -10785,7 +10785,7 @@
     <row r="15">
       <c r="A15" s="14" t="n"/>
       <c r="B15" s="23" t="str">
-        <f>IF(A15="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A15,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A15="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A15,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -10802,7 +10802,7 @@
     <row r="16">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="23" t="str">
-        <f>IF(A16="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A16,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A16="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A16,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -10819,7 +10819,7 @@
     <row r="17">
       <c r="A17" s="14" t="n"/>
       <c r="B17" s="23" t="str">
-        <f>IF(A17="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A17,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A17="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A17,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -10836,7 +10836,7 @@
     <row r="18">
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="23" t="str">
-        <f>IF(A18="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A18,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A18="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A18,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -10853,7 +10853,7 @@
     <row r="19">
       <c r="A19" s="14" t="n"/>
       <c r="B19" s="23" t="str">
-        <f>IF(A19="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A19,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A19="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A19,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -10870,7 +10870,7 @@
     <row r="20">
       <c r="A20" s="14" t="n"/>
       <c r="B20" s="23" t="str">
-        <f>IF(A20="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A20,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A20="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A20,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -10887,7 +10887,7 @@
     <row r="21">
       <c r="A21" s="14" t="n"/>
       <c r="B21" s="23" t="str">
-        <f>IF(A21="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A21,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A21="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A21,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -10904,7 +10904,7 @@
     <row r="22">
       <c r="A22" s="14" t="n"/>
       <c r="B22" s="23" t="str">
-        <f>IF(A22="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A22,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A22="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A22,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -10921,7 +10921,7 @@
     <row r="23">
       <c r="A23" s="14" t="n"/>
       <c r="B23" s="23" t="str">
-        <f>IF(A23="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A23,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A23="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A23,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -10938,7 +10938,7 @@
     <row r="24">
       <c r="A24" s="14" t="n"/>
       <c r="B24" s="23" t="str">
-        <f>IF(A24="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A24,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A24="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A24,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -10955,7 +10955,7 @@
     <row r="25">
       <c r="A25" s="14" t="n"/>
       <c r="B25" s="23" t="str">
-        <f>IF(A25="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A25,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A25="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A25,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -10972,7 +10972,7 @@
     <row r="26">
       <c r="A26" s="14" t="n"/>
       <c r="B26" s="23" t="str">
-        <f>IF(A26="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A26,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A26="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A26,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -10989,7 +10989,7 @@
     <row r="27">
       <c r="A27" s="14" t="n"/>
       <c r="B27" s="23" t="str">
-        <f>IF(A27="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A27,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A27="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A27,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -11006,7 +11006,7 @@
     <row r="28">
       <c r="A28" s="14" t="n"/>
       <c r="B28" s="23" t="str">
-        <f>IF(A28="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A28,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A28="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A28,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -11023,7 +11023,7 @@
     <row r="29">
       <c r="A29" s="14" t="n"/>
       <c r="B29" s="23" t="str">
-        <f>IF(A29="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A29,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A29="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A29,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -11040,7 +11040,7 @@
     <row r="30">
       <c r="A30" s="14" t="n"/>
       <c r="B30" s="23" t="str">
-        <f>IF(A30="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A30,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A30="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A30,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -11057,7 +11057,7 @@
     <row r="31">
       <c r="A31" s="14" t="n"/>
       <c r="B31" s="23" t="str">
-        <f>IF(A31="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A31,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A31="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A31,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C31" s="5" t="n"/>
@@ -11074,7 +11074,7 @@
     <row r="32">
       <c r="A32" s="14" t="n"/>
       <c r="B32" s="23" t="str">
-        <f>IF(A32="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A32,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A32="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A32,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C32" s="5" t="n"/>
@@ -11091,7 +11091,7 @@
     <row r="33">
       <c r="A33" s="14" t="n"/>
       <c r="B33" s="23" t="str">
-        <f>IF(A33="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A33,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A33="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A33,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C33" s="5" t="n"/>
@@ -11108,7 +11108,7 @@
     <row r="34">
       <c r="A34" s="14" t="n"/>
       <c r="B34" s="23" t="str">
-        <f>IF(A34="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A34,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A34="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A34,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C34" s="5" t="n"/>
@@ -11125,7 +11125,7 @@
     <row r="35">
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="23" t="str">
-        <f>IF(A35="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A35,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A35="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A35,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -11142,7 +11142,7 @@
     <row r="36">
       <c r="A36" s="14" t="n"/>
       <c r="B36" s="23" t="str">
-        <f>IF(A36="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A36,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A36="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A36,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C36" s="5" t="n"/>
@@ -11159,7 +11159,7 @@
     <row r="37">
       <c r="A37" s="14" t="n"/>
       <c r="B37" s="23" t="str">
-        <f>IF(A37="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A37,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A37="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A37,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C37" s="5" t="n"/>
@@ -11176,7 +11176,7 @@
     <row r="38">
       <c r="A38" s="14" t="n"/>
       <c r="B38" s="23" t="str">
-        <f>IF(A38="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A38,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A38="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A38,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C38" s="5" t="n"/>
@@ -11193,7 +11193,7 @@
     <row r="39">
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="23" t="str">
-        <f>IF(A39="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A39,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A39="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A39,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C39" s="5" t="n"/>
@@ -11210,7 +11210,7 @@
     <row r="40">
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="23" t="str">
-        <f>IF(A40="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A40,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A40="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A40,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C40" s="5" t="n"/>
@@ -11227,7 +11227,7 @@
     <row r="41">
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="23" t="str">
-        <f>IF(A41="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A41,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A41="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A41,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C41" s="5" t="n"/>
@@ -11244,7 +11244,7 @@
     <row r="42">
       <c r="A42" s="14" t="n"/>
       <c r="B42" s="23" t="str">
-        <f>IF(A42="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A42,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A42="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A42,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C42" s="5" t="n"/>
@@ -11261,7 +11261,7 @@
     <row r="43">
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="23" t="str">
-        <f>IF(A43="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A43,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A43="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A43,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C43" s="5" t="n"/>
@@ -11278,7 +11278,7 @@
     <row r="44">
       <c r="A44" s="14" t="n"/>
       <c r="B44" s="23" t="str">
-        <f>IF(A44="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A44,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A44="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A44,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C44" s="5" t="n"/>
@@ -11295,7 +11295,7 @@
     <row r="45">
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="23" t="str">
-        <f>IF(A45="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A45,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A45="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A45,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C45" s="5" t="n"/>
@@ -11312,7 +11312,7 @@
     <row r="46">
       <c r="A46" s="14" t="n"/>
       <c r="B46" s="23" t="str">
-        <f>IF(A46="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A46,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A46="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A46,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C46" s="5" t="n"/>
@@ -11329,7 +11329,7 @@
     <row r="47">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="23" t="str">
-        <f>IF(A47="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A47,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A47="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A47,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C47" s="5" t="n"/>
@@ -11346,7 +11346,7 @@
     <row r="48">
       <c r="A48" s="14" t="n"/>
       <c r="B48" s="23" t="str">
-        <f>IF(A48="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A48,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A48="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A48,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C48" s="5" t="n"/>
@@ -11363,7 +11363,7 @@
     <row r="49">
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="23" t="str">
-        <f>IF(A49="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A49,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A49="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A49,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C49" s="5" t="n"/>
@@ -11380,7 +11380,7 @@
     <row r="50">
       <c r="A50" s="14" t="n"/>
       <c r="B50" s="23" t="str">
-        <f>IF(A50="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A50,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A50="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A50,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C50" s="5" t="n"/>
@@ -11397,7 +11397,7 @@
     <row r="51">
       <c r="A51" s="14" t="n"/>
       <c r="B51" s="23" t="str">
-        <f>IF(A51="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A51,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A51="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A51,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C51" s="5" t="n"/>
@@ -11414,7 +11414,7 @@
     <row r="52">
       <c r="A52" s="14" t="n"/>
       <c r="B52" s="23" t="str">
-        <f>IF(A52="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A52,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A52="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A52,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C52" s="5" t="n"/>
@@ -11431,7 +11431,7 @@
     <row r="53">
       <c r="A53" s="14" t="n"/>
       <c r="B53" s="23" t="str">
-        <f>IF(A53="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A53,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A53="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A53,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C53" s="5" t="n"/>
@@ -11448,7 +11448,7 @@
     <row r="54">
       <c r="A54" s="14" t="n"/>
       <c r="B54" s="23" t="str">
-        <f>IF(A54="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A54,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A54="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A54,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C54" s="5" t="n"/>
@@ -11465,7 +11465,7 @@
     <row r="55">
       <c r="A55" s="14" t="n"/>
       <c r="B55" s="23" t="str">
-        <f>IF(A55="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A55,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A55="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A55,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C55" s="5" t="n"/>
@@ -11482,7 +11482,7 @@
     <row r="56">
       <c r="A56" s="14" t="n"/>
       <c r="B56" s="23" t="str">
-        <f>IF(A56="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A56,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A56="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A56,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C56" s="5" t="n"/>
@@ -11499,7 +11499,7 @@
     <row r="57">
       <c r="A57" s="14" t="n"/>
       <c r="B57" s="23" t="str">
-        <f>IF(A57="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A57,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A57="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A57,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C57" s="5" t="n"/>
@@ -11516,7 +11516,7 @@
     <row r="58">
       <c r="A58" s="14" t="n"/>
       <c r="B58" s="23" t="str">
-        <f>IF(A58="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A58,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A58="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A58,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C58" s="5" t="n"/>
@@ -11533,7 +11533,7 @@
     <row r="59">
       <c r="A59" s="14" t="n"/>
       <c r="B59" s="23" t="str">
-        <f>IF(A59="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A59,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A59="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A59,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C59" s="5" t="n"/>
@@ -11550,7 +11550,7 @@
     <row r="60">
       <c r="A60" s="14" t="n"/>
       <c r="B60" s="23" t="str">
-        <f>IF(A60="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A60,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A60="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A60,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C60" s="5" t="n"/>
@@ -11567,7 +11567,7 @@
     <row r="61">
       <c r="A61" s="14" t="n"/>
       <c r="B61" s="23" t="str">
-        <f>IF(A61="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A61,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A61="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A61,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C61" s="5" t="n"/>
@@ -11584,7 +11584,7 @@
     <row r="62">
       <c r="A62" s="14" t="n"/>
       <c r="B62" s="23" t="str">
-        <f>IF(A62="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A62,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A62="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A62,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C62" s="5" t="n"/>
@@ -11601,7 +11601,7 @@
     <row r="63">
       <c r="A63" s="14" t="n"/>
       <c r="B63" s="23" t="str">
-        <f>IF(A63="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A63,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A63="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A63,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C63" s="5" t="n"/>
@@ -11618,7 +11618,7 @@
     <row r="64">
       <c r="A64" s="14" t="n"/>
       <c r="B64" s="23" t="str">
-        <f>IF(A64="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A64,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A64="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A64,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C64" s="5" t="n"/>
@@ -11635,7 +11635,7 @@
     <row r="65">
       <c r="A65" s="14" t="n"/>
       <c r="B65" s="23" t="str">
-        <f>IF(A65="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A65,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A65="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A65,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C65" s="5" t="n"/>
@@ -11652,7 +11652,7 @@
     <row r="66">
       <c r="A66" s="14" t="n"/>
       <c r="B66" s="23" t="str">
-        <f>IF(A66="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A66,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A66="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A66,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C66" s="5" t="n"/>
@@ -11669,7 +11669,7 @@
     <row r="67">
       <c r="A67" s="14" t="n"/>
       <c r="B67" s="23" t="str">
-        <f>IF(A67="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A67,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A67="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A67,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C67" s="5" t="n"/>
@@ -11686,7 +11686,7 @@
     <row r="68">
       <c r="A68" s="14" t="n"/>
       <c r="B68" s="23" t="str">
-        <f>IF(A68="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A68,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A68="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A68,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C68" s="5" t="n"/>
@@ -11703,7 +11703,7 @@
     <row r="69">
       <c r="A69" s="14" t="n"/>
       <c r="B69" s="23" t="str">
-        <f>IF(A69="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A69,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A69="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A69,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C69" s="5" t="n"/>
@@ -11720,7 +11720,7 @@
     <row r="70">
       <c r="A70" s="14" t="n"/>
       <c r="B70" s="23" t="str">
-        <f>IF(A70="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A70,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A70="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A70,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C70" s="5" t="n"/>
@@ -11737,7 +11737,7 @@
     <row r="71">
       <c r="A71" s="14" t="n"/>
       <c r="B71" s="23" t="str">
-        <f>IF(A71="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A71,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A71="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A71,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C71" s="5" t="n"/>
@@ -11754,7 +11754,7 @@
     <row r="72">
       <c r="A72" s="14" t="n"/>
       <c r="B72" s="23" t="str">
-        <f>IF(A72="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A72,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A72="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A72,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C72" s="5" t="n"/>
@@ -11771,7 +11771,7 @@
     <row r="73">
       <c r="A73" s="14" t="n"/>
       <c r="B73" s="23" t="str">
-        <f>IF(A73="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A73,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A73="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A73,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C73" s="5" t="n"/>
@@ -11788,7 +11788,7 @@
     <row r="74">
       <c r="A74" s="14" t="n"/>
       <c r="B74" s="23" t="str">
-        <f>IF(A74="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A74,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A74="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A74,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C74" s="5" t="n"/>
@@ -11805,7 +11805,7 @@
     <row r="75">
       <c r="A75" s="14" t="n"/>
       <c r="B75" s="23" t="str">
-        <f>IF(A75="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A75,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A75="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A75,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C75" s="5" t="n"/>
@@ -11822,7 +11822,7 @@
     <row r="76">
       <c r="A76" s="14" t="n"/>
       <c r="B76" s="23" t="str">
-        <f>IF(A76="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A76,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A76="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A76,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C76" s="5" t="n"/>
@@ -11839,7 +11839,7 @@
     <row r="77">
       <c r="A77" s="14" t="n"/>
       <c r="B77" s="23" t="str">
-        <f>IF(A77="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A77,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A77="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A77,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C77" s="5" t="n"/>
@@ -11856,7 +11856,7 @@
     <row r="78">
       <c r="A78" s="14" t="n"/>
       <c r="B78" s="23" t="str">
-        <f>IF(A78="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A78,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A78="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A78,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C78" s="5" t="n"/>
@@ -11873,7 +11873,7 @@
     <row r="79">
       <c r="A79" s="14" t="n"/>
       <c r="B79" s="23" t="str">
-        <f>IF(A79="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A79,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A79="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A79,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C79" s="5" t="n"/>
@@ -11890,7 +11890,7 @@
     <row r="80">
       <c r="A80" s="14" t="n"/>
       <c r="B80" s="23" t="str">
-        <f>IF(A80="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A80,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A80="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A80,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C80" s="5" t="n"/>
@@ -11907,7 +11907,7 @@
     <row r="81">
       <c r="A81" s="14" t="n"/>
       <c r="B81" s="23" t="str">
-        <f>IF(A81="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A81,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A81="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A81,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C81" s="5" t="n"/>
@@ -11924,7 +11924,7 @@
     <row r="82">
       <c r="A82" s="14" t="n"/>
       <c r="B82" s="23" t="str">
-        <f>IF(A82="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A82,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A82="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A82,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C82" s="5" t="n"/>
@@ -11941,7 +11941,7 @@
     <row r="83">
       <c r="A83" s="14" t="n"/>
       <c r="B83" s="23" t="str">
-        <f>IF(A83="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A83,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A83="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A83,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C83" s="5" t="n"/>
@@ -11958,7 +11958,7 @@
     <row r="84">
       <c r="A84" s="14" t="n"/>
       <c r="B84" s="23" t="str">
-        <f>IF(A84="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A84,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A84="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A84,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C84" s="5" t="n"/>
@@ -11975,7 +11975,7 @@
     <row r="85">
       <c r="A85" s="14" t="n"/>
       <c r="B85" s="23" t="str">
-        <f>IF(A85="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A85,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A85="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A85,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C85" s="5" t="n"/>
@@ -11992,7 +11992,7 @@
     <row r="86">
       <c r="A86" s="14" t="n"/>
       <c r="B86" s="23" t="str">
-        <f>IF(A86="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A86,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A86="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A86,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C86" s="5" t="n"/>
@@ -12009,7 +12009,7 @@
     <row r="87">
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="23" t="str">
-        <f>IF(A87="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A87,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A87="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A87,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C87" s="5" t="n"/>
@@ -12026,7 +12026,7 @@
     <row r="88">
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="23" t="str">
-        <f>IF(A88="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A88,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A88="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A88,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C88" s="5" t="n"/>
@@ -12043,7 +12043,7 @@
     <row r="89">
       <c r="A89" s="14" t="n"/>
       <c r="B89" s="23" t="str">
-        <f>IF(A89="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A89,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A89="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A89,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C89" s="5" t="n"/>
@@ -12060,7 +12060,7 @@
     <row r="90">
       <c r="A90" s="14" t="n"/>
       <c r="B90" s="23" t="str">
-        <f>IF(A90="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A90,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A90="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A90,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C90" s="5" t="n"/>
@@ -12077,7 +12077,7 @@
     <row r="91">
       <c r="A91" s="14" t="n"/>
       <c r="B91" s="23" t="str">
-        <f>IF(A91="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A91,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A91="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A91,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C91" s="5" t="n"/>
@@ -12094,7 +12094,7 @@
     <row r="92">
       <c r="A92" s="14" t="n"/>
       <c r="B92" s="23" t="str">
-        <f>IF(A92="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A92,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A92="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A92,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C92" s="5" t="n"/>
@@ -12111,7 +12111,7 @@
     <row r="93">
       <c r="A93" s="14" t="n"/>
       <c r="B93" s="23" t="str">
-        <f>IF(A93="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A93,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A93="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A93,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C93" s="5" t="n"/>
@@ -12128,7 +12128,7 @@
     <row r="94">
       <c r="A94" s="14" t="n"/>
       <c r="B94" s="23" t="str">
-        <f>IF(A94="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A94,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A94="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A94,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C94" s="5" t="n"/>
@@ -12145,7 +12145,7 @@
     <row r="95">
       <c r="A95" s="14" t="n"/>
       <c r="B95" s="23" t="str">
-        <f>IF(A95="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A95,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A95="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A95,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C95" s="5" t="n"/>
@@ -12162,7 +12162,7 @@
     <row r="96">
       <c r="A96" s="14" t="n"/>
       <c r="B96" s="23" t="str">
-        <f>IF(A96="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A96,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A96="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A96,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C96" s="5" t="n"/>
@@ -12179,7 +12179,7 @@
     <row r="97">
       <c r="A97" s="14" t="n"/>
       <c r="B97" s="23" t="str">
-        <f>IF(A97="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A97,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A97="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A97,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C97" s="5" t="n"/>
@@ -12196,7 +12196,7 @@
     <row r="98">
       <c r="A98" s="14" t="n"/>
       <c r="B98" s="23" t="str">
-        <f>IF(A98="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A98,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A98="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A98,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C98" s="5" t="n"/>
@@ -12213,7 +12213,7 @@
     <row r="99">
       <c r="A99" s="14" t="n"/>
       <c r="B99" s="23" t="str">
-        <f>IF(A99="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A99,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A99="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A99,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C99" s="5" t="n"/>
@@ -12230,7 +12230,7 @@
     <row r="100">
       <c r="A100" s="14" t="n"/>
       <c r="B100" s="23" t="str">
-        <f>IF(A100="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A100,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A100="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A100,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C100" s="5" t="n"/>
@@ -12247,7 +12247,7 @@
     <row r="101">
       <c r="A101" s="14" t="n"/>
       <c r="B101" s="23" t="str">
-        <f>IF(A101="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A101,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A101="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A101,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C101" s="5" t="n"/>
@@ -12264,7 +12264,7 @@
     <row r="102">
       <c r="A102" s="14" t="n"/>
       <c r="B102" s="23" t="str">
-        <f>IF(A102="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A102,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A102="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A102,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C102" s="5" t="n"/>
@@ -12281,7 +12281,7 @@
     <row r="103">
       <c r="A103" s="14" t="n"/>
       <c r="B103" s="23" t="str">
-        <f>IF(A103="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A103,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A103="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A103,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C103" s="5" t="n"/>
@@ -12298,7 +12298,7 @@
     <row r="104">
       <c r="A104" s="14" t="n"/>
       <c r="B104" s="23" t="str">
-        <f>IF(A104="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A104,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A104="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A104,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C104" s="5" t="n"/>
@@ -12315,7 +12315,7 @@
     <row r="105">
       <c r="A105" s="14" t="n"/>
       <c r="B105" s="23" t="str">
-        <f>IF(A105="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A105,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A105="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A105,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C105" s="5" t="n"/>
@@ -12332,7 +12332,7 @@
     <row r="106">
       <c r="A106" s="14" t="n"/>
       <c r="B106" s="23" t="str">
-        <f>IF(A106="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A106,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A106="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A106,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C106" s="5" t="n"/>
@@ -12349,7 +12349,7 @@
     <row r="107">
       <c r="A107" s="14" t="n"/>
       <c r="B107" s="23" t="str">
-        <f>IF(A107="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A107,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A107="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A107,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C107" s="5" t="n"/>
@@ -12366,7 +12366,7 @@
     <row r="108">
       <c r="A108" s="14" t="n"/>
       <c r="B108" s="23" t="str">
-        <f>IF(A108="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A108,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A108="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A108,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C108" s="5" t="n"/>
@@ -12383,7 +12383,7 @@
     <row r="109">
       <c r="A109" s="14" t="n"/>
       <c r="B109" s="23" t="str">
-        <f>IF(A109="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A109,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A109="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A109,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C109" s="5" t="n"/>
@@ -12400,7 +12400,7 @@
     <row r="110">
       <c r="A110" s="14" t="n"/>
       <c r="B110" s="23" t="str">
-        <f>IF(A110="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A110,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A110="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A110,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C110" s="5" t="n"/>
@@ -12417,7 +12417,7 @@
     <row r="111">
       <c r="A111" s="14" t="n"/>
       <c r="B111" s="23" t="str">
-        <f>IF(A111="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A111,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A111="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A111,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C111" s="5" t="n"/>
@@ -12434,7 +12434,7 @@
     <row r="112">
       <c r="A112" s="14" t="n"/>
       <c r="B112" s="23" t="str">
-        <f>IF(A112="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A112,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A112="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A112,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C112" s="5" t="n"/>
@@ -12451,7 +12451,7 @@
     <row r="113">
       <c r="A113" s="14" t="n"/>
       <c r="B113" s="23" t="str">
-        <f>IF(A113="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A113,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A113="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A113,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C113" s="5" t="n"/>
@@ -12468,7 +12468,7 @@
     <row r="114">
       <c r="A114" s="14" t="n"/>
       <c r="B114" s="23" t="str">
-        <f>IF(A114="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A114,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A114="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A114,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C114" s="5" t="n"/>
@@ -12485,7 +12485,7 @@
     <row r="115">
       <c r="A115" s="14" t="n"/>
       <c r="B115" s="23" t="str">
-        <f>IF(A115="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A115,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A115="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A115,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C115" s="5" t="n"/>
@@ -12502,7 +12502,7 @@
     <row r="116">
       <c r="A116" s="14" t="n"/>
       <c r="B116" s="23" t="str">
-        <f>IF(A116="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A116,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A116="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A116,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C116" s="5" t="n"/>
@@ -12519,7 +12519,7 @@
     <row r="117">
       <c r="A117" s="14" t="n"/>
       <c r="B117" s="23" t="str">
-        <f>IF(A117="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A117,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A117="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A117,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C117" s="5" t="n"/>
@@ -12536,7 +12536,7 @@
     <row r="118">
       <c r="A118" s="14" t="n"/>
       <c r="B118" s="23" t="str">
-        <f>IF(A118="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A118,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A118="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A118,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C118" s="5" t="n"/>
@@ -12553,7 +12553,7 @@
     <row r="119">
       <c r="A119" s="14" t="n"/>
       <c r="B119" s="23" t="str">
-        <f>IF(A119="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A119,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A119="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A119,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C119" s="5" t="n"/>
@@ -12570,7 +12570,7 @@
     <row r="120">
       <c r="A120" s="14" t="n"/>
       <c r="B120" s="23" t="str">
-        <f>IF(A120="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A120,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A120="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A120,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C120" s="5" t="n"/>
@@ -12587,7 +12587,7 @@
     <row r="121">
       <c r="A121" s="14" t="n"/>
       <c r="B121" s="23" t="str">
-        <f>IF(A121="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A121,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A121="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A121,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C121" s="5" t="n"/>
@@ -12604,7 +12604,7 @@
     <row r="122">
       <c r="A122" s="14" t="n"/>
       <c r="B122" s="23" t="str">
-        <f>IF(A122="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A122,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A122="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A122,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C122" s="5" t="n"/>
@@ -12621,7 +12621,7 @@
     <row r="123">
       <c r="A123" s="14" t="n"/>
       <c r="B123" s="23" t="str">
-        <f>IF(A123="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A123,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A123="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A123,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C123" s="5" t="n"/>
@@ -12638,7 +12638,7 @@
     <row r="124">
       <c r="A124" s="14" t="n"/>
       <c r="B124" s="23" t="str">
-        <f>IF(A124="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A124,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A124="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A124,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C124" s="5" t="n"/>
@@ -12655,7 +12655,7 @@
     <row r="125">
       <c r="A125" s="14" t="n"/>
       <c r="B125" s="23" t="str">
-        <f>IF(A125="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A125,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A125="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A125,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C125" s="5" t="n"/>
@@ -12672,7 +12672,7 @@
     <row r="126">
       <c r="A126" s="14" t="n"/>
       <c r="B126" s="23" t="str">
-        <f>IF(A126="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A126,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A126="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A126,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C126" s="5" t="n"/>
@@ -12689,7 +12689,7 @@
     <row r="127">
       <c r="A127" s="14" t="n"/>
       <c r="B127" s="23" t="str">
-        <f>IF(A127="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A127,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A127="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A127,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C127" s="5" t="n"/>
@@ -12706,7 +12706,7 @@
     <row r="128">
       <c r="A128" s="14" t="n"/>
       <c r="B128" s="23" t="str">
-        <f>IF(A128="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A128,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A128="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A128,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C128" s="5" t="n"/>
@@ -12723,7 +12723,7 @@
     <row r="129">
       <c r="A129" s="14" t="n"/>
       <c r="B129" s="23" t="str">
-        <f>IF(A129="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A129,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A129="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A129,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C129" s="5" t="n"/>
@@ -12740,7 +12740,7 @@
     <row r="130">
       <c r="A130" s="14" t="n"/>
       <c r="B130" s="23" t="str">
-        <f>IF(A130="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A130,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A130="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A130,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C130" s="5" t="n"/>
@@ -12757,7 +12757,7 @@
     <row r="131">
       <c r="A131" s="14" t="n"/>
       <c r="B131" s="23" t="str">
-        <f>IF(A131="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A131,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A131="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A131,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C131" s="5" t="n"/>
@@ -12774,7 +12774,7 @@
     <row r="132">
       <c r="A132" s="14" t="n"/>
       <c r="B132" s="23" t="str">
-        <f>IF(A132="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A132,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A132="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A132,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C132" s="5" t="n"/>
@@ -12791,7 +12791,7 @@
     <row r="133">
       <c r="A133" s="14" t="n"/>
       <c r="B133" s="23" t="str">
-        <f>IF(A133="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A133,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A133="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A133,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C133" s="5" t="n"/>
@@ -12808,7 +12808,7 @@
     <row r="134">
       <c r="A134" s="14" t="n"/>
       <c r="B134" s="23" t="str">
-        <f>IF(A134="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A134,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A134="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A134,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C134" s="5" t="n"/>
@@ -12825,7 +12825,7 @@
     <row r="135">
       <c r="A135" s="14" t="n"/>
       <c r="B135" s="23" t="str">
-        <f>IF(A135="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A135,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A135="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A135,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C135" s="5" t="n"/>
@@ -12842,7 +12842,7 @@
     <row r="136">
       <c r="A136" s="14" t="n"/>
       <c r="B136" s="23" t="str">
-        <f>IF(A136="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A136,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A136="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A136,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C136" s="5" t="n"/>
@@ -12859,7 +12859,7 @@
     <row r="137">
       <c r="A137" s="14" t="n"/>
       <c r="B137" s="23" t="str">
-        <f>IF(A137="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A137,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A137="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A137,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C137" s="5" t="n"/>
@@ -12876,7 +12876,7 @@
     <row r="138">
       <c r="A138" s="14" t="n"/>
       <c r="B138" s="23" t="str">
-        <f>IF(A138="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A138,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A138="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A138,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C138" s="5" t="n"/>
@@ -12893,7 +12893,7 @@
     <row r="139">
       <c r="A139" s="14" t="n"/>
       <c r="B139" s="23" t="str">
-        <f>IF(A139="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A139,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A139="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A139,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C139" s="5" t="n"/>
@@ -12910,7 +12910,7 @@
     <row r="140">
       <c r="A140" s="14" t="n"/>
       <c r="B140" s="23" t="str">
-        <f>IF(A140="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A140,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A140="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A140,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C140" s="5" t="n"/>
@@ -12927,7 +12927,7 @@
     <row r="141">
       <c r="A141" s="14" t="n"/>
       <c r="B141" s="23" t="str">
-        <f>IF(A141="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A141,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A141="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A141,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C141" s="5" t="n"/>
@@ -12944,7 +12944,7 @@
     <row r="142">
       <c r="A142" s="14" t="n"/>
       <c r="B142" s="23" t="str">
-        <f>IF(A142="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A142,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A142="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A142,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C142" s="5" t="n"/>
@@ -12961,7 +12961,7 @@
     <row r="143">
       <c r="A143" s="14" t="n"/>
       <c r="B143" s="23" t="str">
-        <f>IF(A143="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A143,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A143="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A143,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C143" s="5" t="n"/>
@@ -12978,7 +12978,7 @@
     <row r="144">
       <c r="A144" s="14" t="n"/>
       <c r="B144" s="23" t="str">
-        <f>IF(A144="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A144,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A144="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A144,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C144" s="5" t="n"/>
@@ -12995,7 +12995,7 @@
     <row r="145">
       <c r="A145" s="14" t="n"/>
       <c r="B145" s="23" t="str">
-        <f>IF(A145="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A145,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A145="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A145,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C145" s="5" t="n"/>
@@ -13012,7 +13012,7 @@
     <row r="146">
       <c r="A146" s="14" t="n"/>
       <c r="B146" s="23" t="str">
-        <f>IF(A146="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A146,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A146="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A146,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C146" s="5" t="n"/>
@@ -13029,7 +13029,7 @@
     <row r="147">
       <c r="A147" s="14" t="n"/>
       <c r="B147" s="23" t="str">
-        <f>IF(A147="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A147,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A147="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A147,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C147" s="5" t="n"/>
@@ -13046,7 +13046,7 @@
     <row r="148">
       <c r="A148" s="14" t="n"/>
       <c r="B148" s="23" t="str">
-        <f>IF(A148="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A148,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A148="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A148,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C148" s="5" t="n"/>
@@ -13063,7 +13063,7 @@
     <row r="149">
       <c r="A149" s="14" t="n"/>
       <c r="B149" s="23" t="str">
-        <f>IF(A149="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A149,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A149="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A149,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C149" s="5" t="n"/>
@@ -13080,7 +13080,7 @@
     <row r="150">
       <c r="A150" s="14" t="n"/>
       <c r="B150" s="23" t="str">
-        <f>IF(A150="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A150,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A150="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A150,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C150" s="5" t="n"/>
@@ -13097,7 +13097,7 @@
     <row r="151">
       <c r="A151" s="14" t="n"/>
       <c r="B151" s="23" t="str">
-        <f>IF(A151="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A151,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A151="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A151,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C151" s="5" t="n"/>
@@ -13114,7 +13114,7 @@
     <row r="152">
       <c r="A152" s="14" t="n"/>
       <c r="B152" s="23" t="str">
-        <f>IF(A152="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A152,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A152="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A152,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C152" s="5" t="n"/>
@@ -13131,7 +13131,7 @@
     <row r="153">
       <c r="A153" s="14" t="n"/>
       <c r="B153" s="23" t="str">
-        <f>IF(A153="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A153,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A153="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A153,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C153" s="5" t="n"/>
@@ -13148,7 +13148,7 @@
     <row r="154">
       <c r="A154" s="14" t="n"/>
       <c r="B154" s="23" t="str">
-        <f>IF(A154="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A154,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A154="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A154,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C154" s="5" t="n"/>
@@ -13165,7 +13165,7 @@
     <row r="155">
       <c r="A155" s="14" t="n"/>
       <c r="B155" s="23" t="str">
-        <f>IF(A155="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A155,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A155="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A155,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C155" s="5" t="n"/>
@@ -13182,7 +13182,7 @@
     <row r="156">
       <c r="A156" s="14" t="n"/>
       <c r="B156" s="23" t="str">
-        <f>IF(A156="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A156,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A156="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A156,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C156" s="5" t="n"/>
@@ -13199,7 +13199,7 @@
     <row r="157">
       <c r="A157" s="14" t="n"/>
       <c r="B157" s="23" t="str">
-        <f>IF(A157="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A157,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A157="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A157,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C157" s="5" t="n"/>
@@ -13216,7 +13216,7 @@
     <row r="158">
       <c r="A158" s="14" t="n"/>
       <c r="B158" s="23" t="str">
-        <f>IF(A158="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A158,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A158="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A158,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C158" s="5" t="n"/>
@@ -13233,7 +13233,7 @@
     <row r="159">
       <c r="A159" s="14" t="n"/>
       <c r="B159" s="23" t="str">
-        <f>IF(A159="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A159,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A159="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A159,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C159" s="5" t="n"/>
@@ -13250,7 +13250,7 @@
     <row r="160">
       <c r="A160" s="14" t="n"/>
       <c r="B160" s="23" t="str">
-        <f>IF(A160="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A160,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A160="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A160,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C160" s="5" t="n"/>
@@ -13267,7 +13267,7 @@
     <row r="161">
       <c r="A161" s="14" t="n"/>
       <c r="B161" s="23" t="str">
-        <f>IF(A161="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A161,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A161="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A161,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C161" s="5" t="n"/>
@@ -13284,7 +13284,7 @@
     <row r="162">
       <c r="A162" s="14" t="n"/>
       <c r="B162" s="23" t="str">
-        <f>IF(A162="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A162,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A162="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A162,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C162" s="5" t="n"/>
@@ -13301,7 +13301,7 @@
     <row r="163">
       <c r="A163" s="14" t="n"/>
       <c r="B163" s="23" t="str">
-        <f>IF(A163="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A163,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A163="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A163,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C163" s="5" t="n"/>
@@ -13318,7 +13318,7 @@
     <row r="164">
       <c r="A164" s="14" t="n"/>
       <c r="B164" s="23" t="str">
-        <f>IF(A164="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A164,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A164="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A164,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C164" s="5" t="n"/>
@@ -13335,7 +13335,7 @@
     <row r="165">
       <c r="A165" s="14" t="n"/>
       <c r="B165" s="23" t="str">
-        <f>IF(A165="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A165,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A165="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A165,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C165" s="5" t="n"/>
@@ -13352,7 +13352,7 @@
     <row r="166">
       <c r="A166" s="14" t="n"/>
       <c r="B166" s="23" t="str">
-        <f>IF(A166="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A166,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A166="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A166,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C166" s="5" t="n"/>
@@ -13369,7 +13369,7 @@
     <row r="167">
       <c r="A167" s="14" t="n"/>
       <c r="B167" s="23" t="str">
-        <f>IF(A167="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A167,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A167="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A167,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C167" s="5" t="n"/>
@@ -13386,7 +13386,7 @@
     <row r="168">
       <c r="A168" s="14" t="n"/>
       <c r="B168" s="23" t="str">
-        <f>IF(A168="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A168,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A168="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A168,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C168" s="5" t="n"/>
@@ -13403,7 +13403,7 @@
     <row r="169">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="23" t="str">
-        <f>IF(A169="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A169,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A169="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A169,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C169" s="5" t="n"/>
@@ -13420,7 +13420,7 @@
     <row r="170">
       <c r="A170" s="14" t="n"/>
       <c r="B170" s="23" t="str">
-        <f>IF(A170="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A170,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A170="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A170,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C170" s="5" t="n"/>
@@ -13437,7 +13437,7 @@
     <row r="171">
       <c r="A171" s="14" t="n"/>
       <c r="B171" s="23" t="str">
-        <f>IF(A171="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A171,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A171="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A171,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C171" s="5" t="n"/>
@@ -13454,7 +13454,7 @@
     <row r="172">
       <c r="A172" s="14" t="n"/>
       <c r="B172" s="23" t="str">
-        <f>IF(A172="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A172,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A172="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A172,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C172" s="5" t="n"/>
@@ -13471,7 +13471,7 @@
     <row r="173">
       <c r="A173" s="14" t="n"/>
       <c r="B173" s="23" t="str">
-        <f>IF(A173="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A173,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A173="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A173,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C173" s="5" t="n"/>
@@ -13488,7 +13488,7 @@
     <row r="174">
       <c r="A174" s="14" t="n"/>
       <c r="B174" s="23" t="str">
-        <f>IF(A174="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A174,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A174="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A174,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C174" s="5" t="n"/>
@@ -13505,7 +13505,7 @@
     <row r="175">
       <c r="A175" s="14" t="n"/>
       <c r="B175" s="23" t="str">
-        <f>IF(A175="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A175,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A175="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A175,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C175" s="5" t="n"/>
@@ -13522,7 +13522,7 @@
     <row r="176">
       <c r="A176" s="14" t="n"/>
       <c r="B176" s="23" t="str">
-        <f>IF(A176="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A176,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A176="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A176,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C176" s="5" t="n"/>
@@ -13539,7 +13539,7 @@
     <row r="177">
       <c r="A177" s="14" t="n"/>
       <c r="B177" s="23" t="str">
-        <f>IF(A177="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A177,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A177="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A177,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C177" s="5" t="n"/>
@@ -13556,7 +13556,7 @@
     <row r="178">
       <c r="A178" s="14" t="n"/>
       <c r="B178" s="23" t="str">
-        <f>IF(A178="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A178,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A178="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A178,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C178" s="5" t="n"/>
@@ -13573,7 +13573,7 @@
     <row r="179">
       <c r="A179" s="14" t="n"/>
       <c r="B179" s="23" t="str">
-        <f>IF(A179="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A179,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A179="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A179,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C179" s="5" t="n"/>
@@ -13590,7 +13590,7 @@
     <row r="180">
       <c r="A180" s="14" t="n"/>
       <c r="B180" s="23" t="str">
-        <f>IF(A180="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A180,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A180="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A180,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C180" s="5" t="n"/>
@@ -13607,7 +13607,7 @@
     <row r="181">
       <c r="A181" s="14" t="n"/>
       <c r="B181" s="23" t="str">
-        <f>IF(A181="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A181,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A181="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A181,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C181" s="5" t="n"/>
@@ -13624,7 +13624,7 @@
     <row r="182">
       <c r="A182" s="14" t="n"/>
       <c r="B182" s="23" t="str">
-        <f>IF(A182="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A182,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A182="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A182,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C182" s="5" t="n"/>
@@ -13641,7 +13641,7 @@
     <row r="183">
       <c r="A183" s="14" t="n"/>
       <c r="B183" s="23" t="str">
-        <f>IF(A183="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A183,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A183="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A183,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C183" s="5" t="n"/>
@@ -13658,7 +13658,7 @@
     <row r="184">
       <c r="A184" s="14" t="n"/>
       <c r="B184" s="23" t="str">
-        <f>IF(A184="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A184,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A184="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A184,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C184" s="5" t="n"/>
@@ -13675,7 +13675,7 @@
     <row r="185">
       <c r="A185" s="14" t="n"/>
       <c r="B185" s="23" t="str">
-        <f>IF(A185="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A185,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A185="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A185,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C185" s="5" t="n"/>
@@ -13692,7 +13692,7 @@
     <row r="186">
       <c r="A186" s="14" t="n"/>
       <c r="B186" s="23" t="str">
-        <f>IF(A186="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A186,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A186="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A186,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C186" s="5" t="n"/>
@@ -13709,7 +13709,7 @@
     <row r="187">
       <c r="A187" s="14" t="n"/>
       <c r="B187" s="23" t="str">
-        <f>IF(A187="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A187,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A187="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A187,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C187" s="5" t="n"/>
@@ -13726,7 +13726,7 @@
     <row r="188">
       <c r="A188" s="14" t="n"/>
       <c r="B188" s="23" t="str">
-        <f>IF(A188="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A188,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A188="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A188,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C188" s="5" t="n"/>
@@ -13743,7 +13743,7 @@
     <row r="189">
       <c r="A189" s="14" t="n"/>
       <c r="B189" s="23" t="str">
-        <f>IF(A189="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A189,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A189="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A189,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C189" s="5" t="n"/>
@@ -13760,7 +13760,7 @@
     <row r="190">
       <c r="A190" s="14" t="n"/>
       <c r="B190" s="23" t="str">
-        <f>IF(A190="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A190,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A190="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A190,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C190" s="5" t="n"/>
@@ -13777,7 +13777,7 @@
     <row r="191">
       <c r="A191" s="14" t="n"/>
       <c r="B191" s="23" t="str">
-        <f>IF(A191="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A191,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A191="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A191,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C191" s="5" t="n"/>
@@ -13794,7 +13794,7 @@
     <row r="192">
       <c r="A192" s="14" t="n"/>
       <c r="B192" s="23" t="str">
-        <f>IF(A192="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A192,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A192="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A192,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C192" s="5" t="n"/>
@@ -13811,7 +13811,7 @@
     <row r="193">
       <c r="A193" s="14" t="n"/>
       <c r="B193" s="23" t="str">
-        <f>IF(A193="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A193,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A193="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A193,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C193" s="5" t="n"/>
@@ -13828,7 +13828,7 @@
     <row r="194">
       <c r="A194" s="14" t="n"/>
       <c r="B194" s="23" t="str">
-        <f>IF(A194="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A194,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A194="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A194,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C194" s="5" t="n"/>
@@ -13845,7 +13845,7 @@
     <row r="195">
       <c r="A195" s="14" t="n"/>
       <c r="B195" s="23" t="str">
-        <f>IF(A195="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A195,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A195="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A195,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C195" s="5" t="n"/>
@@ -13862,7 +13862,7 @@
     <row r="196">
       <c r="A196" s="14" t="n"/>
       <c r="B196" s="23" t="str">
-        <f>IF(A196="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A196,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A196="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A196,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C196" s="5" t="n"/>
@@ -13879,7 +13879,7 @@
     <row r="197">
       <c r="A197" s="14" t="n"/>
       <c r="B197" s="23" t="str">
-        <f>IF(A197="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A197,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A197="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A197,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C197" s="5" t="n"/>
@@ -13896,7 +13896,7 @@
     <row r="198">
       <c r="A198" s="14" t="n"/>
       <c r="B198" s="23" t="str">
-        <f>IF(A198="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A198,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A198="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A198,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C198" s="5" t="n"/>
@@ -13913,7 +13913,7 @@
     <row r="199">
       <c r="A199" s="14" t="n"/>
       <c r="B199" s="23" t="str">
-        <f>IF(A199="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A199,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A199="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A199,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C199" s="5" t="n"/>
@@ -13930,7 +13930,7 @@
     <row r="200">
       <c r="A200" s="14" t="n"/>
       <c r="B200" s="23" t="str">
-        <f>IF(A200="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A200,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A200="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A200,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C200" s="5" t="n"/>
@@ -13947,7 +13947,7 @@
     <row r="201">
       <c r="A201" s="14" t="n"/>
       <c r="B201" s="23" t="str">
-        <f>IF(A201="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A201,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A201="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A201,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C201" s="5" t="n"/>
@@ -13964,7 +13964,7 @@
     <row r="202">
       <c r="A202" s="14" t="n"/>
       <c r="B202" s="23" t="str">
-        <f>IF(A202="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A202,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A202="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A202,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C202" s="5" t="n"/>
@@ -13981,7 +13981,7 @@
     <row r="203">
       <c r="A203" s="14" t="n"/>
       <c r="B203" s="23" t="str">
-        <f>IF(A203="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A203,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A203="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A203,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C203" s="5" t="n"/>
@@ -13998,7 +13998,7 @@
     <row r="204">
       <c r="A204" s="14" t="n"/>
       <c r="B204" s="23" t="str">
-        <f>IF(A204="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A204,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A204="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A204,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C204" s="5" t="n"/>
@@ -14015,7 +14015,7 @@
     <row r="205">
       <c r="A205" s="14" t="n"/>
       <c r="B205" s="23" t="str">
-        <f>IF(A205="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A205,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A205="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A205,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C205" s="5" t="n"/>
@@ -14032,7 +14032,7 @@
     <row r="206">
       <c r="A206" s="14" t="n"/>
       <c r="B206" s="23" t="str">
-        <f>IF(A206="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A206,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A206="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A206,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C206" s="5" t="n"/>
@@ -14049,7 +14049,7 @@
     <row r="207">
       <c r="A207" s="14" t="n"/>
       <c r="B207" s="23" t="str">
-        <f>IF(A207="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A207,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A207="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A207,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C207" s="5" t="n"/>
@@ -14066,7 +14066,7 @@
     <row r="208">
       <c r="A208" s="14" t="n"/>
       <c r="B208" s="23" t="str">
-        <f>IF(A208="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A208,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A208="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A208,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C208" s="5" t="n"/>
@@ -14083,7 +14083,7 @@
     <row r="209">
       <c r="A209" s="14" t="n"/>
       <c r="B209" s="23" t="str">
-        <f>IF(A209="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A209,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A209="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A209,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C209" s="5" t="n"/>
@@ -14100,7 +14100,7 @@
     <row r="210">
       <c r="A210" s="14" t="n"/>
       <c r="B210" s="23" t="str">
-        <f>IF(A210="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A210,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A210="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A210,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C210" s="5" t="n"/>
@@ -14117,7 +14117,7 @@
     <row r="211">
       <c r="A211" s="14" t="n"/>
       <c r="B211" s="23" t="str">
-        <f>IF(A211="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A211,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A211="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A211,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C211" s="5" t="n"/>
@@ -14134,7 +14134,7 @@
     <row r="212">
       <c r="A212" s="14" t="n"/>
       <c r="B212" s="23" t="str">
-        <f>IF(A212="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A212,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A212="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A212,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C212" s="5" t="n"/>
@@ -14151,7 +14151,7 @@
     <row r="213">
       <c r="A213" s="14" t="n"/>
       <c r="B213" s="23" t="str">
-        <f>IF(A213="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A213,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A213="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A213,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C213" s="5" t="n"/>
@@ -14168,7 +14168,7 @@
     <row r="214">
       <c r="A214" s="14" t="n"/>
       <c r="B214" s="23" t="str">
-        <f>IF(A214="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A214,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A214="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A214,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C214" s="5" t="n"/>
@@ -14185,7 +14185,7 @@
     <row r="215">
       <c r="A215" s="14" t="n"/>
       <c r="B215" s="23" t="str">
-        <f>IF(A215="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A215,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A215="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A215,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C215" s="5" t="n"/>
@@ -14202,7 +14202,7 @@
     <row r="216">
       <c r="A216" s="14" t="n"/>
       <c r="B216" s="23" t="str">
-        <f>IF(A216="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A216,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A216="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A216,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C216" s="5" t="n"/>
@@ -14219,7 +14219,7 @@
     <row r="217">
       <c r="A217" s="14" t="n"/>
       <c r="B217" s="23" t="str">
-        <f>IF(A217="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A217,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A217="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A217,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C217" s="5" t="n"/>
@@ -14236,7 +14236,7 @@
     <row r="218">
       <c r="A218" s="14" t="n"/>
       <c r="B218" s="23" t="str">
-        <f>IF(A218="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A218,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A218="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A218,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C218" s="5" t="n"/>
@@ -14253,7 +14253,7 @@
     <row r="219">
       <c r="A219" s="14" t="n"/>
       <c r="B219" s="23" t="str">
-        <f>IF(A219="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A219,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A219="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A219,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C219" s="5" t="n"/>
@@ -14270,7 +14270,7 @@
     <row r="220">
       <c r="A220" s="14" t="n"/>
       <c r="B220" s="23" t="str">
-        <f>IF(A220="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A220,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A220="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A220,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C220" s="5" t="n"/>
@@ -14287,7 +14287,7 @@
     <row r="221">
       <c r="A221" s="14" t="n"/>
       <c r="B221" s="23" t="str">
-        <f>IF(A221="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A221,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A221="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A221,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C221" s="5" t="n"/>
@@ -14304,7 +14304,7 @@
     <row r="222">
       <c r="A222" s="14" t="n"/>
       <c r="B222" s="23" t="str">
-        <f>IF(A222="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A222,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A222="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A222,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C222" s="5" t="n"/>
@@ -14321,7 +14321,7 @@
     <row r="223">
       <c r="A223" s="14" t="n"/>
       <c r="B223" s="23" t="str">
-        <f>IF(A223="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A223,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A223="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A223,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C223" s="5" t="n"/>
@@ -14338,7 +14338,7 @@
     <row r="224">
       <c r="A224" s="14" t="n"/>
       <c r="B224" s="23" t="str">
-        <f>IF(A224="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A224,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A224="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A224,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C224" s="5" t="n"/>
@@ -14355,7 +14355,7 @@
     <row r="225">
       <c r="A225" s="14" t="n"/>
       <c r="B225" s="23" t="str">
-        <f>IF(A225="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A225,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A225="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A225,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C225" s="5" t="n"/>
@@ -14372,7 +14372,7 @@
     <row r="226">
       <c r="A226" s="14" t="n"/>
       <c r="B226" s="23" t="str">
-        <f>IF(A226="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A226,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A226="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A226,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C226" s="5" t="n"/>
@@ -14389,7 +14389,7 @@
     <row r="227">
       <c r="A227" s="14" t="n"/>
       <c r="B227" s="23" t="str">
-        <f>IF(A227="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A227,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A227="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A227,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C227" s="5" t="n"/>
@@ -14406,7 +14406,7 @@
     <row r="228">
       <c r="A228" s="14" t="n"/>
       <c r="B228" s="23" t="str">
-        <f>IF(A228="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A228,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A228="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A228,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C228" s="5" t="n"/>
@@ -14423,7 +14423,7 @@
     <row r="229">
       <c r="A229" s="14" t="n"/>
       <c r="B229" s="23" t="str">
-        <f>IF(A229="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A229,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A229="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A229,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C229" s="5" t="n"/>
@@ -14440,7 +14440,7 @@
     <row r="230">
       <c r="A230" s="14" t="n"/>
       <c r="B230" s="23" t="str">
-        <f>IF(A230="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A230,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A230="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A230,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C230" s="5" t="n"/>
@@ -14457,7 +14457,7 @@
     <row r="231">
       <c r="A231" s="14" t="n"/>
       <c r="B231" s="23" t="str">
-        <f>IF(A231="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A231,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A231="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A231,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C231" s="5" t="n"/>
@@ -14474,7 +14474,7 @@
     <row r="232">
       <c r="A232" s="14" t="n"/>
       <c r="B232" s="23" t="str">
-        <f>IF(A232="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A232,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A232="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A232,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C232" s="5" t="n"/>
@@ -14491,7 +14491,7 @@
     <row r="233">
       <c r="A233" s="14" t="n"/>
       <c r="B233" s="23" t="str">
-        <f>IF(A233="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A233,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A233="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A233,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C233" s="5" t="n"/>
@@ -14508,7 +14508,7 @@
     <row r="234">
       <c r="A234" s="14" t="n"/>
       <c r="B234" s="23" t="str">
-        <f>IF(A234="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A234,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A234="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A234,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C234" s="5" t="n"/>
@@ -14525,7 +14525,7 @@
     <row r="235">
       <c r="A235" s="14" t="n"/>
       <c r="B235" s="23" t="str">
-        <f>IF(A235="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A235,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A235="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A235,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C235" s="5" t="n"/>
@@ -14542,7 +14542,7 @@
     <row r="236">
       <c r="A236" s="14" t="n"/>
       <c r="B236" s="23" t="str">
-        <f>IF(A236="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A236,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A236="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A236,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C236" s="5" t="n"/>
@@ -14559,7 +14559,7 @@
     <row r="237">
       <c r="A237" s="14" t="n"/>
       <c r="B237" s="23" t="str">
-        <f>IF(A237="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A237,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A237="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A237,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C237" s="5" t="n"/>
@@ -14576,7 +14576,7 @@
     <row r="238">
       <c r="A238" s="14" t="n"/>
       <c r="B238" s="23" t="str">
-        <f>IF(A238="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A238,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A238="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A238,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C238" s="5" t="n"/>
@@ -14593,7 +14593,7 @@
     <row r="239">
       <c r="A239" s="14" t="n"/>
       <c r="B239" s="23" t="str">
-        <f>IF(A239="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A239,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A239="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A239,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C239" s="5" t="n"/>
@@ -14610,7 +14610,7 @@
     <row r="240">
       <c r="A240" s="14" t="n"/>
       <c r="B240" s="23" t="str">
-        <f>IF(A240="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A240,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A240="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A240,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C240" s="5" t="n"/>
@@ -14627,7 +14627,7 @@
     <row r="241">
       <c r="A241" s="14" t="n"/>
       <c r="B241" s="23" t="str">
-        <f>IF(A241="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A241,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A241="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A241,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C241" s="5" t="n"/>
@@ -14644,7 +14644,7 @@
     <row r="242">
       <c r="A242" s="14" t="n"/>
       <c r="B242" s="23" t="str">
-        <f>IF(A242="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A242,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A242="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A242,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C242" s="5" t="n"/>
@@ -14661,7 +14661,7 @@
     <row r="243">
       <c r="A243" s="14" t="n"/>
       <c r="B243" s="23" t="str">
-        <f>IF(A243="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A243,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A243="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A243,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C243" s="5" t="n"/>
@@ -14678,7 +14678,7 @@
     <row r="244">
       <c r="A244" s="14" t="n"/>
       <c r="B244" s="23" t="str">
-        <f>IF(A244="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A244,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A244="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A244,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C244" s="5" t="n"/>
@@ -14695,7 +14695,7 @@
     <row r="245">
       <c r="A245" s="14" t="n"/>
       <c r="B245" s="23" t="str">
-        <f>IF(A245="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A245,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A245="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A245,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C245" s="5" t="n"/>
@@ -14712,7 +14712,7 @@
     <row r="246">
       <c r="A246" s="14" t="n"/>
       <c r="B246" s="23" t="str">
-        <f>IF(A246="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A246,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A246="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A246,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C246" s="5" t="n"/>
@@ -14729,7 +14729,7 @@
     <row r="247">
       <c r="A247" s="14" t="n"/>
       <c r="B247" s="23" t="str">
-        <f>IF(A247="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A247,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A247="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A247,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C247" s="5" t="n"/>
@@ -14746,7 +14746,7 @@
     <row r="248">
       <c r="A248" s="14" t="n"/>
       <c r="B248" s="23" t="str">
-        <f>IF(A248="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A248,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A248="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A248,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C248" s="5" t="n"/>
@@ -14763,7 +14763,7 @@
     <row r="249">
       <c r="A249" s="14" t="n"/>
       <c r="B249" s="23" t="str">
-        <f>IF(A249="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A249,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A249="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A249,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C249" s="5" t="n"/>
@@ -14780,7 +14780,7 @@
     <row r="250">
       <c r="A250" s="14" t="n"/>
       <c r="B250" s="23" t="str">
-        <f>IF(A250="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A250,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A250="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A250,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C250" s="5" t="n"/>
@@ -14797,7 +14797,7 @@
     <row r="251">
       <c r="A251" s="14" t="n"/>
       <c r="B251" s="23" t="str">
-        <f>IF(A251="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A251,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A251="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A251,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C251" s="5" t="n"/>
@@ -14814,7 +14814,7 @@
     <row r="252">
       <c r="A252" s="14" t="n"/>
       <c r="B252" s="23" t="str">
-        <f>IF(A252="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A252,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A252="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A252,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C252" s="5" t="n"/>
@@ -14831,7 +14831,7 @@
     <row r="253">
       <c r="A253" s="14" t="n"/>
       <c r="B253" s="23" t="str">
-        <f>IF(A253="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A253,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A253="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A253,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C253" s="5" t="n"/>
@@ -14848,7 +14848,7 @@
     <row r="254">
       <c r="A254" s="14" t="n"/>
       <c r="B254" s="23" t="str">
-        <f>IF(A254="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A254,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A254="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A254,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C254" s="5" t="n"/>
@@ -14865,7 +14865,7 @@
     <row r="255">
       <c r="A255" s="14" t="n"/>
       <c r="B255" s="23" t="str">
-        <f>IF(A255="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A255,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A255="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A255,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C255" s="5" t="n"/>
@@ -14882,7 +14882,7 @@
     <row r="256">
       <c r="A256" s="14" t="n"/>
       <c r="B256" s="23" t="str">
-        <f>IF(A256="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A256,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A256="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A256,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C256" s="5" t="n"/>
@@ -14899,7 +14899,7 @@
     <row r="257">
       <c r="A257" s="14" t="n"/>
       <c r="B257" s="23" t="str">
-        <f>IF(A257="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A257,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A257="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A257,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C257" s="5" t="n"/>
@@ -14916,7 +14916,7 @@
     <row r="258">
       <c r="A258" s="14" t="n"/>
       <c r="B258" s="23" t="str">
-        <f>IF(A258="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A258,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A258="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A258,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C258" s="5" t="n"/>
@@ -14933,7 +14933,7 @@
     <row r="259">
       <c r="A259" s="14" t="n"/>
       <c r="B259" s="23" t="str">
-        <f>IF(A259="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A259,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A259="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A259,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C259" s="5" t="n"/>
@@ -14950,7 +14950,7 @@
     <row r="260">
       <c r="A260" s="14" t="n"/>
       <c r="B260" s="23" t="str">
-        <f>IF(A260="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A260,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A260="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A260,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C260" s="5" t="n"/>
@@ -14967,7 +14967,7 @@
     <row r="261">
       <c r="A261" s="14" t="n"/>
       <c r="B261" s="23" t="str">
-        <f>IF(A261="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A261,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A261="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A261,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C261" s="5" t="n"/>
@@ -14984,7 +14984,7 @@
     <row r="262">
       <c r="A262" s="14" t="n"/>
       <c r="B262" s="23" t="str">
-        <f>IF(A262="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A262,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A262="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A262,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C262" s="5" t="n"/>
@@ -15001,7 +15001,7 @@
     <row r="263">
       <c r="A263" s="14" t="n"/>
       <c r="B263" s="23" t="str">
-        <f>IF(A263="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A263,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A263="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A263,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C263" s="5" t="n"/>
@@ -15018,7 +15018,7 @@
     <row r="264">
       <c r="A264" s="14" t="n"/>
       <c r="B264" s="23" t="str">
-        <f>IF(A264="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A264,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A264="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A264,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C264" s="5" t="n"/>
@@ -15035,7 +15035,7 @@
     <row r="265">
       <c r="A265" s="14" t="n"/>
       <c r="B265" s="23" t="str">
-        <f>IF(A265="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A265,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A265="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A265,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C265" s="5" t="n"/>
@@ -15052,7 +15052,7 @@
     <row r="266">
       <c r="A266" s="14" t="n"/>
       <c r="B266" s="23" t="str">
-        <f>IF(A266="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A266,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A266="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A266,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C266" s="5" t="n"/>
@@ -15069,7 +15069,7 @@
     <row r="267">
       <c r="A267" s="14" t="n"/>
       <c r="B267" s="23" t="str">
-        <f>IF(A267="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A267,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A267="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A267,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C267" s="5" t="n"/>
@@ -15086,7 +15086,7 @@
     <row r="268">
       <c r="A268" s="14" t="n"/>
       <c r="B268" s="23" t="str">
-        <f>IF(A268="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A268,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A268="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A268,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C268" s="5" t="n"/>
@@ -15103,7 +15103,7 @@
     <row r="269">
       <c r="A269" s="14" t="n"/>
       <c r="B269" s="23" t="str">
-        <f>IF(A269="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A269,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A269="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A269,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C269" s="5" t="n"/>
@@ -15120,7 +15120,7 @@
     <row r="270">
       <c r="A270" s="14" t="n"/>
       <c r="B270" s="23" t="str">
-        <f>IF(A270="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A270,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A270="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A270,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C270" s="5" t="n"/>
@@ -15137,7 +15137,7 @@
     <row r="271">
       <c r="A271" s="14" t="n"/>
       <c r="B271" s="23" t="str">
-        <f>IF(A271="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A271,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A271="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A271,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C271" s="5" t="n"/>
@@ -15154,7 +15154,7 @@
     <row r="272">
       <c r="A272" s="14" t="n"/>
       <c r="B272" s="23" t="str">
-        <f>IF(A272="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A272,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A272="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A272,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C272" s="5" t="n"/>
@@ -15171,7 +15171,7 @@
     <row r="273">
       <c r="A273" s="14" t="n"/>
       <c r="B273" s="23" t="str">
-        <f>IF(A273="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A273,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A273="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A273,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C273" s="5" t="n"/>
@@ -15188,7 +15188,7 @@
     <row r="274">
       <c r="A274" s="14" t="n"/>
       <c r="B274" s="23" t="str">
-        <f>IF(A274="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A274,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A274="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A274,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C274" s="5" t="n"/>
@@ -15205,7 +15205,7 @@
     <row r="275">
       <c r="A275" s="14" t="n"/>
       <c r="B275" s="23" t="str">
-        <f>IF(A275="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A275,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A275="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A275,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C275" s="5" t="n"/>
@@ -15222,7 +15222,7 @@
     <row r="276">
       <c r="A276" s="14" t="n"/>
       <c r="B276" s="23" t="str">
-        <f>IF(A276="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A276,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A276="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A276,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C276" s="5" t="n"/>
@@ -15239,7 +15239,7 @@
     <row r="277">
       <c r="A277" s="14" t="n"/>
       <c r="B277" s="23" t="str">
-        <f>IF(A277="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A277,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A277="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A277,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C277" s="5" t="n"/>
@@ -15256,7 +15256,7 @@
     <row r="278">
       <c r="A278" s="14" t="n"/>
       <c r="B278" s="23" t="str">
-        <f>IF(A278="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A278,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A278="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A278,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C278" s="5" t="n"/>
@@ -15273,7 +15273,7 @@
     <row r="279">
       <c r="A279" s="14" t="n"/>
       <c r="B279" s="23" t="str">
-        <f>IF(A279="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A279,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A279="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A279,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C279" s="5" t="n"/>
@@ -15290,7 +15290,7 @@
     <row r="280">
       <c r="A280" s="14" t="n"/>
       <c r="B280" s="23" t="str">
-        <f>IF(A280="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A280,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A280="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A280,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C280" s="5" t="n"/>
@@ -15307,7 +15307,7 @@
     <row r="281">
       <c r="A281" s="14" t="n"/>
       <c r="B281" s="23" t="str">
-        <f>IF(A281="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A281,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A281="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A281,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C281" s="5" t="n"/>
@@ -15324,7 +15324,7 @@
     <row r="282">
       <c r="A282" s="14" t="n"/>
       <c r="B282" s="23" t="str">
-        <f>IF(A282="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A282,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A282="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A282,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C282" s="5" t="n"/>
@@ -15341,7 +15341,7 @@
     <row r="283">
       <c r="A283" s="14" t="n"/>
       <c r="B283" s="23" t="str">
-        <f>IF(A283="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A283,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A283="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A283,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C283" s="5" t="n"/>
@@ -15358,7 +15358,7 @@
     <row r="284">
       <c r="A284" s="14" t="n"/>
       <c r="B284" s="23" t="str">
-        <f>IF(A284="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A284,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A284="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A284,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C284" s="5" t="n"/>
@@ -15375,7 +15375,7 @@
     <row r="285">
       <c r="A285" s="14" t="n"/>
       <c r="B285" s="23" t="str">
-        <f>IF(A285="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A285,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A285="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A285,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C285" s="5" t="n"/>
@@ -15392,7 +15392,7 @@
     <row r="286">
       <c r="A286" s="14" t="n"/>
       <c r="B286" s="23" t="str">
-        <f>IF(A286="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A286,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A286="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A286,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C286" s="5" t="n"/>
@@ -15409,7 +15409,7 @@
     <row r="287">
       <c r="A287" s="14" t="n"/>
       <c r="B287" s="23" t="str">
-        <f>IF(A287="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A287,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A287="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A287,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C287" s="5" t="n"/>
@@ -15426,7 +15426,7 @@
     <row r="288">
       <c r="A288" s="14" t="n"/>
       <c r="B288" s="23" t="str">
-        <f>IF(A288="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A288,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A288="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A288,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C288" s="5" t="n"/>
@@ -15443,7 +15443,7 @@
     <row r="289">
       <c r="A289" s="14" t="n"/>
       <c r="B289" s="23" t="str">
-        <f>IF(A289="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A289,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A289="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A289,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C289" s="5" t="n"/>
@@ -15460,7 +15460,7 @@
     <row r="290">
       <c r="A290" s="14" t="n"/>
       <c r="B290" s="23" t="str">
-        <f>IF(A290="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A290,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A290="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A290,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C290" s="5" t="n"/>
@@ -15477,7 +15477,7 @@
     <row r="291">
       <c r="A291" s="14" t="n"/>
       <c r="B291" s="23" t="str">
-        <f>IF(A291="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A291,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A291="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A291,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C291" s="5" t="n"/>
@@ -15494,7 +15494,7 @@
     <row r="292">
       <c r="A292" s="14" t="n"/>
       <c r="B292" s="23" t="str">
-        <f>IF(A292="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A292,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A292="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A292,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C292" s="5" t="n"/>
@@ -15511,7 +15511,7 @@
     <row r="293">
       <c r="A293" s="14" t="n"/>
       <c r="B293" s="23" t="str">
-        <f>IF(A293="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A293,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A293="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A293,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C293" s="5" t="n"/>
@@ -15528,7 +15528,7 @@
     <row r="294">
       <c r="A294" s="14" t="n"/>
       <c r="B294" s="23" t="str">
-        <f>IF(A294="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A294,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A294="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A294,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C294" s="5" t="n"/>
@@ -15545,7 +15545,7 @@
     <row r="295">
       <c r="A295" s="14" t="n"/>
       <c r="B295" s="23" t="str">
-        <f>IF(A295="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A295,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A295="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A295,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C295" s="5" t="n"/>
@@ -15562,7 +15562,7 @@
     <row r="296">
       <c r="A296" s="14" t="n"/>
       <c r="B296" s="23" t="str">
-        <f>IF(A296="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A296,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A296="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A296,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C296" s="5" t="n"/>
@@ -15579,7 +15579,7 @@
     <row r="297">
       <c r="A297" s="14" t="n"/>
       <c r="B297" s="23" t="str">
-        <f>IF(A297="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A297,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A297="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A297,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C297" s="5" t="n"/>
@@ -15596,7 +15596,7 @@
     <row r="298">
       <c r="A298" s="14" t="n"/>
       <c r="B298" s="23" t="str">
-        <f>IF(A298="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A298,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A298="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A298,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C298" s="5" t="n"/>
@@ -15613,7 +15613,7 @@
     <row r="299">
       <c r="A299" s="14" t="n"/>
       <c r="B299" s="23" t="str">
-        <f>IF(A299="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A299,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A299="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A299,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C299" s="5" t="n"/>
@@ -15630,7 +15630,7 @@
     <row r="300">
       <c r="A300" s="14" t="n"/>
       <c r="B300" s="23" t="str">
-        <f>IF(A300="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A300,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A300="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A300,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C300" s="5" t="n"/>
@@ -15647,7 +15647,7 @@
     <row r="301">
       <c r="A301" s="14" t="n"/>
       <c r="B301" s="23" t="str">
-        <f>IF(A301="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A301,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A301="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A301,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C301" s="5" t="n"/>
@@ -15664,7 +15664,7 @@
     <row r="302">
       <c r="A302" s="14" t="n"/>
       <c r="B302" s="23" t="str">
-        <f>IF(A302="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A302,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A302="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A302,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C302" s="5" t="n"/>
@@ -15681,7 +15681,7 @@
     <row r="303">
       <c r="A303" s="14" t="n"/>
       <c r="B303" s="23" t="str">
-        <f>IF(A303="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A303,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A303="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A303,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C303" s="5" t="n"/>
@@ -15698,7 +15698,7 @@
     <row r="304">
       <c r="A304" s="14" t="n"/>
       <c r="B304" s="23" t="str">
-        <f>IF(A304="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A304,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A304="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A304,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C304" s="5" t="n"/>
@@ -15715,7 +15715,7 @@
     <row r="305">
       <c r="A305" s="14" t="n"/>
       <c r="B305" s="23" t="str">
-        <f>IF(A305="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A305,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A305="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A305,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C305" s="5" t="n"/>
@@ -15732,7 +15732,7 @@
     <row r="306">
       <c r="A306" s="14" t="n"/>
       <c r="B306" s="23" t="str">
-        <f>IF(A306="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A306,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A306="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A306,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C306" s="5" t="n"/>
@@ -15749,7 +15749,7 @@
     <row r="307">
       <c r="A307" s="14" t="n"/>
       <c r="B307" s="23" t="str">
-        <f>IF(A307="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A307,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A307="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A307,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C307" s="5" t="n"/>
@@ -15766,7 +15766,7 @@
     <row r="308">
       <c r="A308" s="14" t="n"/>
       <c r="B308" s="23" t="str">
-        <f>IF(A308="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A308,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A308="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A308,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C308" s="5" t="n"/>
@@ -15783,7 +15783,7 @@
     <row r="309">
       <c r="A309" s="14" t="n"/>
       <c r="B309" s="23" t="str">
-        <f>IF(A309="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A309,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A309="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A309,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C309" s="5" t="n"/>
@@ -15800,7 +15800,7 @@
     <row r="310">
       <c r="A310" s="14" t="n"/>
       <c r="B310" s="23" t="str">
-        <f>IF(A310="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A310,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A310="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A310,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C310" s="5" t="n"/>
@@ -15817,7 +15817,7 @@
     <row r="311">
       <c r="A311" s="14" t="n"/>
       <c r="B311" s="23" t="str">
-        <f>IF(A311="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A311,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A311="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A311,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C311" s="5" t="n"/>
@@ -15834,7 +15834,7 @@
     <row r="312">
       <c r="A312" s="14" t="n"/>
       <c r="B312" s="23" t="str">
-        <f>IF(A312="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A312,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A312="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A312,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C312" s="5" t="n"/>
@@ -15851,7 +15851,7 @@
     <row r="313">
       <c r="A313" s="14" t="n"/>
       <c r="B313" s="23" t="str">
-        <f>IF(A313="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A313,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A313="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A313,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C313" s="5" t="n"/>
@@ -15868,7 +15868,7 @@
     <row r="314">
       <c r="A314" s="14" t="n"/>
       <c r="B314" s="23" t="str">
-        <f>IF(A314="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A314,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A314="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A314,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C314" s="5" t="n"/>
@@ -15885,7 +15885,7 @@
     <row r="315">
       <c r="A315" s="14" t="n"/>
       <c r="B315" s="23" t="str">
-        <f>IF(A315="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A315,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A315="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A315,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C315" s="5" t="n"/>
@@ -15902,7 +15902,7 @@
     <row r="316">
       <c r="A316" s="14" t="n"/>
       <c r="B316" s="23" t="str">
-        <f>IF(A316="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A316,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A316="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A316,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C316" s="5" t="n"/>
@@ -15919,7 +15919,7 @@
     <row r="317">
       <c r="A317" s="14" t="n"/>
       <c r="B317" s="23" t="str">
-        <f>IF(A317="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A317,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A317="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A317,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C317" s="5" t="n"/>
@@ -15936,7 +15936,7 @@
     <row r="318">
       <c r="A318" s="14" t="n"/>
       <c r="B318" s="23" t="str">
-        <f>IF(A318="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A318,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A318="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A318,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C318" s="5" t="n"/>
@@ -15953,7 +15953,7 @@
     <row r="319">
       <c r="A319" s="14" t="n"/>
       <c r="B319" s="23" t="str">
-        <f>IF(A319="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A319,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A319="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A319,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C319" s="5" t="n"/>
@@ -15970,7 +15970,7 @@
     <row r="320">
       <c r="A320" s="14" t="n"/>
       <c r="B320" s="23" t="str">
-        <f>IF(A320="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A320,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A320="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A320,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C320" s="5" t="n"/>
@@ -15987,7 +15987,7 @@
     <row r="321">
       <c r="A321" s="14" t="n"/>
       <c r="B321" s="23" t="str">
-        <f>IF(A321="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A321,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A321="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A321,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C321" s="5" t="n"/>
@@ -16004,7 +16004,7 @@
     <row r="322">
       <c r="A322" s="14" t="n"/>
       <c r="B322" s="23" t="str">
-        <f>IF(A322="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A322,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A322="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A322,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C322" s="5" t="n"/>
@@ -16021,7 +16021,7 @@
     <row r="323">
       <c r="A323" s="14" t="n"/>
       <c r="B323" s="23" t="str">
-        <f>IF(A323="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A323,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A323="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A323,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C323" s="5" t="n"/>
@@ -16038,7 +16038,7 @@
     <row r="324">
       <c r="A324" s="14" t="n"/>
       <c r="B324" s="23" t="str">
-        <f>IF(A324="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A324,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A324="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A324,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C324" s="5" t="n"/>
@@ -16055,7 +16055,7 @@
     <row r="325">
       <c r="A325" s="14" t="n"/>
       <c r="B325" s="23" t="str">
-        <f>IF(A325="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A325,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A325="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A325,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C325" s="5" t="n"/>
@@ -16072,7 +16072,7 @@
     <row r="326">
       <c r="A326" s="14" t="n"/>
       <c r="B326" s="23" t="str">
-        <f>IF(A326="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A326,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A326="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A326,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C326" s="5" t="n"/>
@@ -16089,7 +16089,7 @@
     <row r="327">
       <c r="A327" s="14" t="n"/>
       <c r="B327" s="23" t="str">
-        <f>IF(A327="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A327,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A327="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A327,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C327" s="5" t="n"/>
@@ -16106,7 +16106,7 @@
     <row r="328">
       <c r="A328" s="14" t="n"/>
       <c r="B328" s="23" t="str">
-        <f>IF(A328="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A328,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A328="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A328,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C328" s="5" t="n"/>
@@ -16123,7 +16123,7 @@
     <row r="329">
       <c r="A329" s="14" t="n"/>
       <c r="B329" s="23" t="str">
-        <f>IF(A329="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A329,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A329="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A329,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C329" s="5" t="n"/>
@@ -16140,7 +16140,7 @@
     <row r="330">
       <c r="A330" s="14" t="n"/>
       <c r="B330" s="23" t="str">
-        <f>IF(A330="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A330,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A330="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A330,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C330" s="5" t="n"/>
@@ -16157,7 +16157,7 @@
     <row r="331">
       <c r="A331" s="14" t="n"/>
       <c r="B331" s="23" t="str">
-        <f>IF(A331="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A331,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A331="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A331,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C331" s="5" t="n"/>
@@ -16174,7 +16174,7 @@
     <row r="332">
       <c r="A332" s="14" t="n"/>
       <c r="B332" s="23" t="str">
-        <f>IF(A332="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A332,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A332="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A332,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C332" s="5" t="n"/>
@@ -16191,7 +16191,7 @@
     <row r="333">
       <c r="A333" s="14" t="n"/>
       <c r="B333" s="23" t="str">
-        <f>IF(A333="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A333,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A333="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A333,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C333" s="5" t="n"/>
@@ -16208,7 +16208,7 @@
     <row r="334">
       <c r="A334" s="14" t="n"/>
       <c r="B334" s="23" t="str">
-        <f>IF(A334="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A334,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A334="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A334,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C334" s="5" t="n"/>
@@ -16225,7 +16225,7 @@
     <row r="335">
       <c r="A335" s="14" t="n"/>
       <c r="B335" s="23" t="str">
-        <f>IF(A335="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A335,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A335="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A335,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C335" s="5" t="n"/>
@@ -16242,7 +16242,7 @@
     <row r="336">
       <c r="A336" s="14" t="n"/>
       <c r="B336" s="23" t="str">
-        <f>IF(A336="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A336,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A336="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A336,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C336" s="5" t="n"/>
@@ -16259,7 +16259,7 @@
     <row r="337">
       <c r="A337" s="14" t="n"/>
       <c r="B337" s="23" t="str">
-        <f>IF(A337="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A337,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A337="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A337,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C337" s="5" t="n"/>
@@ -16276,7 +16276,7 @@
     <row r="338">
       <c r="A338" s="14" t="n"/>
       <c r="B338" s="23" t="str">
-        <f>IF(A338="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A338,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A338="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A338,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C338" s="5" t="n"/>
@@ -16293,7 +16293,7 @@
     <row r="339">
       <c r="A339" s="14" t="n"/>
       <c r="B339" s="23" t="str">
-        <f>IF(A339="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A339,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A339="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A339,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C339" s="5" t="n"/>
@@ -16310,7 +16310,7 @@
     <row r="340">
       <c r="A340" s="14" t="n"/>
       <c r="B340" s="23" t="str">
-        <f>IF(A340="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A340,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A340="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A340,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C340" s="5" t="n"/>
@@ -16327,7 +16327,7 @@
     <row r="341">
       <c r="A341" s="14" t="n"/>
       <c r="B341" s="23" t="str">
-        <f>IF(A341="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A341,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A341="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A341,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C341" s="5" t="n"/>
@@ -16344,7 +16344,7 @@
     <row r="342">
       <c r="A342" s="14" t="n"/>
       <c r="B342" s="23" t="str">
-        <f>IF(A342="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A342,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A342="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A342,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C342" s="5" t="n"/>
@@ -16361,7 +16361,7 @@
     <row r="343">
       <c r="A343" s="14" t="n"/>
       <c r="B343" s="23" t="str">
-        <f>IF(A343="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A343,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A343="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A343,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C343" s="5" t="n"/>
@@ -16378,7 +16378,7 @@
     <row r="344">
       <c r="A344" s="14" t="n"/>
       <c r="B344" s="23" t="str">
-        <f>IF(A344="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A344,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A344="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A344,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C344" s="5" t="n"/>
@@ -16395,7 +16395,7 @@
     <row r="345">
       <c r="A345" s="14" t="n"/>
       <c r="B345" s="23" t="str">
-        <f>IF(A345="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A345,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A345="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A345,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C345" s="5" t="n"/>
@@ -16412,7 +16412,7 @@
     <row r="346">
       <c r="A346" s="14" t="n"/>
       <c r="B346" s="23" t="str">
-        <f>IF(A346="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A346,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A346="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A346,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C346" s="5" t="n"/>
@@ -16429,7 +16429,7 @@
     <row r="347">
       <c r="A347" s="14" t="n"/>
       <c r="B347" s="23" t="str">
-        <f>IF(A347="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A347,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A347="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A347,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C347" s="5" t="n"/>
@@ -16446,7 +16446,7 @@
     <row r="348">
       <c r="A348" s="14" t="n"/>
       <c r="B348" s="23" t="str">
-        <f>IF(A348="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A348,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A348="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A348,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C348" s="5" t="n"/>
@@ -16463,7 +16463,7 @@
     <row r="349">
       <c r="A349" s="14" t="n"/>
       <c r="B349" s="23" t="str">
-        <f>IF(A349="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A349,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A349="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A349,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C349" s="5" t="n"/>
@@ -16480,7 +16480,7 @@
     <row r="350">
       <c r="A350" s="14" t="n"/>
       <c r="B350" s="23" t="str">
-        <f>IF(A350="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A350,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A350="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A350,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C350" s="5" t="n"/>
@@ -16497,7 +16497,7 @@
     <row r="351">
       <c r="A351" s="14" t="n"/>
       <c r="B351" s="23" t="str">
-        <f>IF(A351="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A351,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A351="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A351,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C351" s="5" t="n"/>
@@ -16514,7 +16514,7 @@
     <row r="352">
       <c r="A352" s="14" t="n"/>
       <c r="B352" s="23" t="str">
-        <f>IF(A352="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A352,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A352="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A352,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C352" s="5" t="n"/>
@@ -16531,7 +16531,7 @@
     <row r="353">
       <c r="A353" s="14" t="n"/>
       <c r="B353" s="23" t="str">
-        <f>IF(A353="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A353,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A353="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A353,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C353" s="5" t="n"/>
@@ -16548,7 +16548,7 @@
     <row r="354">
       <c r="A354" s="14" t="n"/>
       <c r="B354" s="23" t="str">
-        <f>IF(A354="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A354,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A354="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A354,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C354" s="5" t="n"/>
@@ -16565,7 +16565,7 @@
     <row r="355">
       <c r="A355" s="14" t="n"/>
       <c r="B355" s="23" t="str">
-        <f>IF(A355="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A355,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A355="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A355,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C355" s="5" t="n"/>
@@ -16582,7 +16582,7 @@
     <row r="356">
       <c r="A356" s="14" t="n"/>
       <c r="B356" s="23" t="str">
-        <f>IF(A356="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A356,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A356="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A356,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C356" s="5" t="n"/>
@@ -16599,7 +16599,7 @@
     <row r="357">
       <c r="A357" s="14" t="n"/>
       <c r="B357" s="23" t="str">
-        <f>IF(A357="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A357,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A357="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A357,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C357" s="5" t="n"/>
@@ -16616,7 +16616,7 @@
     <row r="358">
       <c r="A358" s="14" t="n"/>
       <c r="B358" s="23" t="str">
-        <f>IF(A358="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A358,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A358="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A358,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C358" s="5" t="n"/>
@@ -16633,7 +16633,7 @@
     <row r="359">
       <c r="A359" s="14" t="n"/>
       <c r="B359" s="23" t="str">
-        <f>IF(A359="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A359,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A359="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A359,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C359" s="5" t="n"/>
@@ -16650,7 +16650,7 @@
     <row r="360">
       <c r="A360" s="14" t="n"/>
       <c r="B360" s="23" t="str">
-        <f>IF(A360="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A360,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A360="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A360,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C360" s="5" t="n"/>
@@ -16667,7 +16667,7 @@
     <row r="361">
       <c r="A361" s="14" t="n"/>
       <c r="B361" s="23" t="str">
-        <f>IF(A361="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A361,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A361="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A361,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C361" s="5" t="n"/>
@@ -16684,7 +16684,7 @@
     <row r="362">
       <c r="A362" s="14" t="n"/>
       <c r="B362" s="23" t="str">
-        <f>IF(A362="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A362,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A362="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A362,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C362" s="5" t="n"/>
@@ -16701,7 +16701,7 @@
     <row r="363">
       <c r="A363" s="14" t="n"/>
       <c r="B363" s="23" t="str">
-        <f>IF(A363="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A363,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A363="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A363,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C363" s="5" t="n"/>
@@ -16718,7 +16718,7 @@
     <row r="364">
       <c r="A364" s="14" t="n"/>
       <c r="B364" s="23" t="str">
-        <f>IF(A364="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A364,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A364="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A364,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C364" s="5" t="n"/>
@@ -16735,7 +16735,7 @@
     <row r="365">
       <c r="A365" s="14" t="n"/>
       <c r="B365" s="23" t="str">
-        <f>IF(A365="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A365,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A365="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A365,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C365" s="5" t="n"/>
@@ -16752,7 +16752,7 @@
     <row r="366">
       <c r="A366" s="14" t="n"/>
       <c r="B366" s="23" t="str">
-        <f>IF(A366="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A366,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A366="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A366,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C366" s="5" t="n"/>
@@ -16769,7 +16769,7 @@
     <row r="367">
       <c r="A367" s="14" t="n"/>
       <c r="B367" s="23" t="str">
-        <f>IF(A367="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A367,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A367="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A367,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C367" s="5" t="n"/>
@@ -16786,7 +16786,7 @@
     <row r="368">
       <c r="A368" s="14" t="n"/>
       <c r="B368" s="23" t="str">
-        <f>IF(A368="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A368,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A368="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A368,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C368" s="5" t="n"/>
@@ -16803,7 +16803,7 @@
     <row r="369">
       <c r="A369" s="14" t="n"/>
       <c r="B369" s="23" t="str">
-        <f>IF(A369="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A369,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A369="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A369,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C369" s="5" t="n"/>
@@ -16820,7 +16820,7 @@
     <row r="370">
       <c r="A370" s="14" t="n"/>
       <c r="B370" s="23" t="str">
-        <f>IF(A370="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A370,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A370="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A370,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C370" s="5" t="n"/>
@@ -16837,7 +16837,7 @@
     <row r="371">
       <c r="A371" s="14" t="n"/>
       <c r="B371" s="23" t="str">
-        <f>IF(A371="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A371,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A371="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A371,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C371" s="5" t="n"/>
@@ -16854,7 +16854,7 @@
     <row r="372">
       <c r="A372" s="14" t="n"/>
       <c r="B372" s="23" t="str">
-        <f>IF(A372="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A372,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A372="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A372,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C372" s="5" t="n"/>
@@ -16871,7 +16871,7 @@
     <row r="373">
       <c r="A373" s="14" t="n"/>
       <c r="B373" s="23" t="str">
-        <f>IF(A373="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A373,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A373="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A373,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C373" s="5" t="n"/>
@@ -16888,7 +16888,7 @@
     <row r="374">
       <c r="A374" s="14" t="n"/>
       <c r="B374" s="23" t="str">
-        <f>IF(A374="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A374,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A374="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A374,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C374" s="5" t="n"/>
@@ -16905,7 +16905,7 @@
     <row r="375">
       <c r="A375" s="14" t="n"/>
       <c r="B375" s="23" t="str">
-        <f>IF(A375="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A375,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A375="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A375,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C375" s="5" t="n"/>
@@ -16922,7 +16922,7 @@
     <row r="376">
       <c r="A376" s="14" t="n"/>
       <c r="B376" s="23" t="str">
-        <f>IF(A376="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A376,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A376="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A376,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C376" s="5" t="n"/>
@@ -16939,7 +16939,7 @@
     <row r="377">
       <c r="A377" s="14" t="n"/>
       <c r="B377" s="23" t="str">
-        <f>IF(A377="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A377,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A377="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A377,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C377" s="5" t="n"/>
@@ -16956,7 +16956,7 @@
     <row r="378">
       <c r="A378" s="14" t="n"/>
       <c r="B378" s="23" t="str">
-        <f>IF(A378="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A378,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A378="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A378,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C378" s="5" t="n"/>
@@ -16973,7 +16973,7 @@
     <row r="379">
       <c r="A379" s="14" t="n"/>
       <c r="B379" s="23" t="str">
-        <f>IF(A379="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A379,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A379="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A379,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C379" s="5" t="n"/>
@@ -16990,7 +16990,7 @@
     <row r="380">
       <c r="A380" s="14" t="n"/>
       <c r="B380" s="23" t="str">
-        <f>IF(A380="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A380,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A380="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A380,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C380" s="5" t="n"/>
@@ -17007,7 +17007,7 @@
     <row r="381">
       <c r="A381" s="14" t="n"/>
       <c r="B381" s="23" t="str">
-        <f>IF(A381="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A381,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A381="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A381,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C381" s="5" t="n"/>
@@ -17024,7 +17024,7 @@
     <row r="382">
       <c r="A382" s="14" t="n"/>
       <c r="B382" s="23" t="str">
-        <f>IF(A382="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A382,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A382="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A382,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C382" s="5" t="n"/>
@@ -17041,7 +17041,7 @@
     <row r="383">
       <c r="A383" s="14" t="n"/>
       <c r="B383" s="23" t="str">
-        <f>IF(A383="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A383,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A383="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A383,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C383" s="5" t="n"/>
@@ -17058,7 +17058,7 @@
     <row r="384">
       <c r="A384" s="14" t="n"/>
       <c r="B384" s="23" t="str">
-        <f>IF(A384="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A384,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A384="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A384,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C384" s="5" t="n"/>
@@ -17075,7 +17075,7 @@
     <row r="385">
       <c r="A385" s="14" t="n"/>
       <c r="B385" s="23" t="str">
-        <f>IF(A385="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A385,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A385="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A385,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C385" s="5" t="n"/>
@@ -17092,7 +17092,7 @@
     <row r="386">
       <c r="A386" s="14" t="n"/>
       <c r="B386" s="23" t="str">
-        <f>IF(A386="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A386,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A386="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A386,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C386" s="5" t="n"/>
@@ -17109,7 +17109,7 @@
     <row r="387">
       <c r="A387" s="14" t="n"/>
       <c r="B387" s="23" t="str">
-        <f>IF(A387="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A387,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A387="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A387,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C387" s="5" t="n"/>
@@ -17126,7 +17126,7 @@
     <row r="388">
       <c r="A388" s="14" t="n"/>
       <c r="B388" s="23" t="str">
-        <f>IF(A388="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A388,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A388="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A388,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C388" s="5" t="n"/>
@@ -17143,7 +17143,7 @@
     <row r="389">
       <c r="A389" s="14" t="n"/>
       <c r="B389" s="23" t="str">
-        <f>IF(A389="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A389,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A389="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A389,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C389" s="5" t="n"/>
@@ -17160,7 +17160,7 @@
     <row r="390">
       <c r="A390" s="14" t="n"/>
       <c r="B390" s="23" t="str">
-        <f>IF(A390="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A390,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A390="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A390,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C390" s="5" t="n"/>
@@ -17177,7 +17177,7 @@
     <row r="391">
       <c r="A391" s="14" t="n"/>
       <c r="B391" s="23" t="str">
-        <f>IF(A391="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A391,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A391="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A391,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C391" s="5" t="n"/>
@@ -17194,7 +17194,7 @@
     <row r="392">
       <c r="A392" s="14" t="n"/>
       <c r="B392" s="23" t="str">
-        <f>IF(A392="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A392,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A392="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A392,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C392" s="5" t="n"/>
@@ -17211,7 +17211,7 @@
     <row r="393">
       <c r="A393" s="14" t="n"/>
       <c r="B393" s="23" t="str">
-        <f>IF(A393="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A393,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A393="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A393,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C393" s="5" t="n"/>
@@ -17228,7 +17228,7 @@
     <row r="394">
       <c r="A394" s="14" t="n"/>
       <c r="B394" s="23" t="str">
-        <f>IF(A394="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A394,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A394="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A394,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C394" s="5" t="n"/>
@@ -17245,7 +17245,7 @@
     <row r="395">
       <c r="A395" s="14" t="n"/>
       <c r="B395" s="23" t="str">
-        <f>IF(A395="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A395,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A395="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A395,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C395" s="5" t="n"/>
@@ -17262,7 +17262,7 @@
     <row r="396">
       <c r="A396" s="14" t="n"/>
       <c r="B396" s="23" t="str">
-        <f>IF(A396="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A396,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A396="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A396,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C396" s="5" t="n"/>
@@ -17279,7 +17279,7 @@
     <row r="397">
       <c r="A397" s="14" t="n"/>
       <c r="B397" s="23" t="str">
-        <f>IF(A397="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A397,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A397="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A397,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C397" s="5" t="n"/>
@@ -17296,7 +17296,7 @@
     <row r="398">
       <c r="A398" s="14" t="n"/>
       <c r="B398" s="23" t="str">
-        <f>IF(A398="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A398,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A398="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A398,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C398" s="5" t="n"/>
@@ -17313,7 +17313,7 @@
     <row r="399">
       <c r="A399" s="14" t="n"/>
       <c r="B399" s="23" t="str">
-        <f>IF(A399="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A399,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A399="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A399,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C399" s="5" t="n"/>
@@ -17330,7 +17330,7 @@
     <row r="400">
       <c r="A400" s="14" t="n"/>
       <c r="B400" s="23" t="str">
-        <f>IF(A400="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A400,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A400="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A400,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C400" s="5" t="n"/>
@@ -17347,7 +17347,7 @@
     <row r="401">
       <c r="A401" s="14" t="n"/>
       <c r="B401" s="23" t="str">
-        <f>IF(A401="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A401,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A401="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A401,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C401" s="5" t="n"/>
@@ -17364,7 +17364,7 @@
     <row r="402">
       <c r="A402" s="14" t="n"/>
       <c r="B402" s="23" t="str">
-        <f>IF(A402="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A402,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A402="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A402,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C402" s="5" t="n"/>
@@ -17381,7 +17381,7 @@
     <row r="403">
       <c r="A403" s="14" t="n"/>
       <c r="B403" s="23" t="str">
-        <f>IF(A403="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A403,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A403="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A403,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C403" s="5" t="n"/>
@@ -17398,7 +17398,7 @@
     <row r="404">
       <c r="A404" s="14" t="n"/>
       <c r="B404" s="23" t="str">
-        <f>IF(A404="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A404,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A404="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A404,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C404" s="5" t="n"/>
@@ -17415,7 +17415,7 @@
     <row r="405">
       <c r="A405" s="14" t="n"/>
       <c r="B405" s="23" t="str">
-        <f>IF(A405="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A405,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A405="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A405,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C405" s="5" t="n"/>
@@ -17432,7 +17432,7 @@
     <row r="406">
       <c r="A406" s="14" t="n"/>
       <c r="B406" s="23" t="str">
-        <f>IF(A406="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A406,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A406="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A406,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C406" s="5" t="n"/>
@@ -17449,7 +17449,7 @@
     <row r="407">
       <c r="A407" s="14" t="n"/>
       <c r="B407" s="23" t="str">
-        <f>IF(A407="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A407,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A407="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A407,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C407" s="5" t="n"/>
@@ -17466,7 +17466,7 @@
     <row r="408">
       <c r="A408" s="14" t="n"/>
       <c r="B408" s="23" t="str">
-        <f>IF(A408="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A408,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A408="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A408,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C408" s="5" t="n"/>
@@ -17483,7 +17483,7 @@
     <row r="409">
       <c r="A409" s="14" t="n"/>
       <c r="B409" s="23" t="str">
-        <f>IF(A409="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A409,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A409="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A409,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C409" s="5" t="n"/>
@@ -17500,7 +17500,7 @@
     <row r="410">
       <c r="A410" s="14" t="n"/>
       <c r="B410" s="23" t="str">
-        <f>IF(A410="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A410,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A410="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A410,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C410" s="5" t="n"/>
@@ -17517,7 +17517,7 @@
     <row r="411">
       <c r="A411" s="14" t="n"/>
       <c r="B411" s="23" t="str">
-        <f>IF(A411="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A411,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A411="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A411,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C411" s="5" t="n"/>
@@ -17534,7 +17534,7 @@
     <row r="412">
       <c r="A412" s="14" t="n"/>
       <c r="B412" s="23" t="str">
-        <f>IF(A412="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A412,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A412="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A412,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C412" s="5" t="n"/>
@@ -17551,7 +17551,7 @@
     <row r="413">
       <c r="A413" s="14" t="n"/>
       <c r="B413" s="23" t="str">
-        <f>IF(A413="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A413,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A413="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A413,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C413" s="5" t="n"/>
@@ -17568,7 +17568,7 @@
     <row r="414">
       <c r="A414" s="14" t="n"/>
       <c r="B414" s="23" t="str">
-        <f>IF(A414="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A414,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A414="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A414,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C414" s="5" t="n"/>
@@ -17585,7 +17585,7 @@
     <row r="415">
       <c r="A415" s="14" t="n"/>
       <c r="B415" s="23" t="str">
-        <f>IF(A415="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A415,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A415="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A415,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C415" s="5" t="n"/>
@@ -17602,7 +17602,7 @@
     <row r="416">
       <c r="A416" s="14" t="n"/>
       <c r="B416" s="23" t="str">
-        <f>IF(A416="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A416,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A416="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A416,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C416" s="5" t="n"/>
@@ -17619,7 +17619,7 @@
     <row r="417">
       <c r="A417" s="14" t="n"/>
       <c r="B417" s="23" t="str">
-        <f>IF(A417="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A417,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A417="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A417,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C417" s="5" t="n"/>
@@ -17636,7 +17636,7 @@
     <row r="418">
       <c r="A418" s="14" t="n"/>
       <c r="B418" s="23" t="str">
-        <f>IF(A418="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A418,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A418="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A418,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C418" s="5" t="n"/>
@@ -17653,7 +17653,7 @@
     <row r="419">
       <c r="A419" s="14" t="n"/>
       <c r="B419" s="23" t="str">
-        <f>IF(A419="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A419,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A419="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A419,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C419" s="5" t="n"/>
@@ -17670,7 +17670,7 @@
     <row r="420">
       <c r="A420" s="14" t="n"/>
       <c r="B420" s="23" t="str">
-        <f>IF(A420="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A420,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A420="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A420,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C420" s="5" t="n"/>
@@ -17687,7 +17687,7 @@
     <row r="421">
       <c r="A421" s="14" t="n"/>
       <c r="B421" s="23" t="str">
-        <f>IF(A421="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A421,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A421="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A421,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C421" s="5" t="n"/>
@@ -17704,7 +17704,7 @@
     <row r="422">
       <c r="A422" s="14" t="n"/>
       <c r="B422" s="23" t="str">
-        <f>IF(A422="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A422,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A422="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A422,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C422" s="5" t="n"/>
@@ -17721,7 +17721,7 @@
     <row r="423">
       <c r="A423" s="14" t="n"/>
       <c r="B423" s="23" t="str">
-        <f>IF(A423="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A423,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A423="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A423,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C423" s="5" t="n"/>
@@ -17738,7 +17738,7 @@
     <row r="424">
       <c r="A424" s="14" t="n"/>
       <c r="B424" s="23" t="str">
-        <f>IF(A424="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A424,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A424="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A424,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C424" s="5" t="n"/>
@@ -17755,7 +17755,7 @@
     <row r="425">
       <c r="A425" s="14" t="n"/>
       <c r="B425" s="23" t="str">
-        <f>IF(A425="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A425,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A425="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A425,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C425" s="5" t="n"/>
@@ -17772,7 +17772,7 @@
     <row r="426">
       <c r="A426" s="14" t="n"/>
       <c r="B426" s="23" t="str">
-        <f>IF(A426="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A426,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A426="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A426,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C426" s="5" t="n"/>
@@ -17789,7 +17789,7 @@
     <row r="427">
       <c r="A427" s="14" t="n"/>
       <c r="B427" s="23" t="str">
-        <f>IF(A427="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A427,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A427="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A427,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C427" s="5" t="n"/>
@@ -17806,7 +17806,7 @@
     <row r="428">
       <c r="A428" s="14" t="n"/>
       <c r="B428" s="23" t="str">
-        <f>IF(A428="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A428,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A428="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A428,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C428" s="5" t="n"/>
@@ -17823,7 +17823,7 @@
     <row r="429">
       <c r="A429" s="14" t="n"/>
       <c r="B429" s="23" t="str">
-        <f>IF(A429="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A429,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A429="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A429,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C429" s="5" t="n"/>
@@ -17840,7 +17840,7 @@
     <row r="430">
       <c r="A430" s="14" t="n"/>
       <c r="B430" s="23" t="str">
-        <f>IF(A430="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A430,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A430="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A430,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C430" s="5" t="n"/>
@@ -17857,7 +17857,7 @@
     <row r="431">
       <c r="A431" s="14" t="n"/>
       <c r="B431" s="23" t="str">
-        <f>IF(A431="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A431,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A431="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A431,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C431" s="5" t="n"/>
@@ -17874,7 +17874,7 @@
     <row r="432">
       <c r="A432" s="14" t="n"/>
       <c r="B432" s="23" t="str">
-        <f>IF(A432="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A432,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A432="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A432,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C432" s="5" t="n"/>
@@ -17891,7 +17891,7 @@
     <row r="433">
       <c r="A433" s="14" t="n"/>
       <c r="B433" s="23" t="str">
-        <f>IF(A433="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A433,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A433="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A433,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C433" s="5" t="n"/>
@@ -17908,7 +17908,7 @@
     <row r="434">
       <c r="A434" s="14" t="n"/>
       <c r="B434" s="23" t="str">
-        <f>IF(A434="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A434,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A434="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A434,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C434" s="5" t="n"/>
@@ -17925,7 +17925,7 @@
     <row r="435">
       <c r="A435" s="14" t="n"/>
       <c r="B435" s="23" t="str">
-        <f>IF(A435="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A435,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A435="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A435,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C435" s="5" t="n"/>
@@ -17942,7 +17942,7 @@
     <row r="436">
       <c r="A436" s="14" t="n"/>
       <c r="B436" s="23" t="str">
-        <f>IF(A436="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A436,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A436="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A436,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C436" s="5" t="n"/>
@@ -17959,7 +17959,7 @@
     <row r="437">
       <c r="A437" s="14" t="n"/>
       <c r="B437" s="23" t="str">
-        <f>IF(A437="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A437,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A437="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A437,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C437" s="5" t="n"/>
@@ -17976,7 +17976,7 @@
     <row r="438">
       <c r="A438" s="14" t="n"/>
       <c r="B438" s="23" t="str">
-        <f>IF(A438="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A438,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A438="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A438,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C438" s="5" t="n"/>
@@ -17993,7 +17993,7 @@
     <row r="439">
       <c r="A439" s="14" t="n"/>
       <c r="B439" s="23" t="str">
-        <f>IF(A439="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A439,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A439="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A439,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C439" s="5" t="n"/>
@@ -18010,7 +18010,7 @@
     <row r="440">
       <c r="A440" s="14" t="n"/>
       <c r="B440" s="23" t="str">
-        <f>IF(A440="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A440,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A440="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A440,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C440" s="5" t="n"/>
@@ -18027,7 +18027,7 @@
     <row r="441">
       <c r="A441" s="14" t="n"/>
       <c r="B441" s="23" t="str">
-        <f>IF(A441="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A441,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A441="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A441,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C441" s="5" t="n"/>
@@ -18044,7 +18044,7 @@
     <row r="442">
       <c r="A442" s="14" t="n"/>
       <c r="B442" s="23" t="str">
-        <f>IF(A442="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A442,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A442="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A442,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C442" s="5" t="n"/>
@@ -18061,7 +18061,7 @@
     <row r="443">
       <c r="A443" s="14" t="n"/>
       <c r="B443" s="23" t="str">
-        <f>IF(A443="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A443,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A443="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A443,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C443" s="5" t="n"/>
@@ -18078,7 +18078,7 @@
     <row r="444">
       <c r="A444" s="14" t="n"/>
       <c r="B444" s="23" t="str">
-        <f>IF(A444="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A444,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A444="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A444,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C444" s="5" t="n"/>
@@ -18095,7 +18095,7 @@
     <row r="445">
       <c r="A445" s="14" t="n"/>
       <c r="B445" s="23" t="str">
-        <f>IF(A445="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A445,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A445="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A445,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C445" s="5" t="n"/>
@@ -18112,7 +18112,7 @@
     <row r="446">
       <c r="A446" s="14" t="n"/>
       <c r="B446" s="23" t="str">
-        <f>IF(A446="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A446,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A446="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A446,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C446" s="5" t="n"/>
@@ -18129,7 +18129,7 @@
     <row r="447">
       <c r="A447" s="14" t="n"/>
       <c r="B447" s="23" t="str">
-        <f>IF(A447="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A447,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A447="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A447,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C447" s="5" t="n"/>
@@ -18146,7 +18146,7 @@
     <row r="448">
       <c r="A448" s="14" t="n"/>
       <c r="B448" s="23" t="str">
-        <f>IF(A448="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A448,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A448="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A448,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C448" s="5" t="n"/>
@@ -18163,7 +18163,7 @@
     <row r="449">
       <c r="A449" s="14" t="n"/>
       <c r="B449" s="23" t="str">
-        <f>IF(A449="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A449,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A449="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A449,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C449" s="5" t="n"/>
@@ -18180,7 +18180,7 @@
     <row r="450">
       <c r="A450" s="14" t="n"/>
       <c r="B450" s="23" t="str">
-        <f>IF(A450="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A450,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A450="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A450,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C450" s="5" t="n"/>
@@ -18197,7 +18197,7 @@
     <row r="451">
       <c r="A451" s="14" t="n"/>
       <c r="B451" s="23" t="str">
-        <f>IF(A451="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A451,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A451="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A451,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C451" s="5" t="n"/>
@@ -18214,7 +18214,7 @@
     <row r="452">
       <c r="A452" s="14" t="n"/>
       <c r="B452" s="23" t="str">
-        <f>IF(A452="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A452,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A452="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A452,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C452" s="5" t="n"/>
@@ -18231,7 +18231,7 @@
     <row r="453">
       <c r="A453" s="14" t="n"/>
       <c r="B453" s="23" t="str">
-        <f>IF(A453="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A453,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A453="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A453,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C453" s="5" t="n"/>
@@ -18248,7 +18248,7 @@
     <row r="454">
       <c r="A454" s="14" t="n"/>
       <c r="B454" s="23" t="str">
-        <f>IF(A454="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A454,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A454="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A454,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C454" s="5" t="n"/>
@@ -18265,7 +18265,7 @@
     <row r="455">
       <c r="A455" s="14" t="n"/>
       <c r="B455" s="23" t="str">
-        <f>IF(A455="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A455,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A455="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A455,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C455" s="5" t="n"/>
@@ -18282,7 +18282,7 @@
     <row r="456">
       <c r="A456" s="14" t="n"/>
       <c r="B456" s="23" t="str">
-        <f>IF(A456="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A456,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A456="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A456,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C456" s="5" t="n"/>
@@ -18299,7 +18299,7 @@
     <row r="457">
       <c r="A457" s="14" t="n"/>
       <c r="B457" s="23" t="str">
-        <f>IF(A457="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A457,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A457="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A457,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C457" s="5" t="n"/>
@@ -18316,7 +18316,7 @@
     <row r="458">
       <c r="A458" s="14" t="n"/>
       <c r="B458" s="23" t="str">
-        <f>IF(A458="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A458,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A458="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A458,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C458" s="5" t="n"/>
@@ -18333,7 +18333,7 @@
     <row r="459">
       <c r="A459" s="14" t="n"/>
       <c r="B459" s="23" t="str">
-        <f>IF(A459="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A459,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A459="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A459,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C459" s="5" t="n"/>
@@ -18350,7 +18350,7 @@
     <row r="460">
       <c r="A460" s="14" t="n"/>
       <c r="B460" s="23" t="str">
-        <f>IF(A460="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A460,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A460="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A460,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C460" s="5" t="n"/>
@@ -18367,7 +18367,7 @@
     <row r="461">
       <c r="A461" s="14" t="n"/>
       <c r="B461" s="23" t="str">
-        <f>IF(A461="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A461,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A461="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A461,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C461" s="5" t="n"/>
@@ -18384,7 +18384,7 @@
     <row r="462">
       <c r="A462" s="14" t="n"/>
       <c r="B462" s="23" t="str">
-        <f>IF(A462="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A462,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A462="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A462,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C462" s="5" t="n"/>
@@ -18401,7 +18401,7 @@
     <row r="463">
       <c r="A463" s="14" t="n"/>
       <c r="B463" s="23" t="str">
-        <f>IF(A463="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A463,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A463="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A463,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C463" s="5" t="n"/>
@@ -18418,7 +18418,7 @@
     <row r="464">
       <c r="A464" s="14" t="n"/>
       <c r="B464" s="23" t="str">
-        <f>IF(A464="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A464,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A464="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A464,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C464" s="5" t="n"/>
@@ -18435,7 +18435,7 @@
     <row r="465">
       <c r="A465" s="14" t="n"/>
       <c r="B465" s="23" t="str">
-        <f>IF(A465="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A465,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A465="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A465,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C465" s="5" t="n"/>
@@ -18452,7 +18452,7 @@
     <row r="466">
       <c r="A466" s="14" t="n"/>
       <c r="B466" s="23" t="str">
-        <f>IF(A466="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A466,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A466="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A466,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C466" s="5" t="n"/>
@@ -18469,7 +18469,7 @@
     <row r="467">
       <c r="A467" s="14" t="n"/>
       <c r="B467" s="23" t="str">
-        <f>IF(A467="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A467,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A467="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A467,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C467" s="5" t="n"/>
@@ -18486,7 +18486,7 @@
     <row r="468">
       <c r="A468" s="14" t="n"/>
       <c r="B468" s="23" t="str">
-        <f>IF(A468="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A468,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A468="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A468,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C468" s="5" t="n"/>
@@ -18503,7 +18503,7 @@
     <row r="469">
       <c r="A469" s="14" t="n"/>
       <c r="B469" s="23" t="str">
-        <f>IF(A469="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A469,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A469="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A469,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C469" s="5" t="n"/>
@@ -18520,7 +18520,7 @@
     <row r="470">
       <c r="A470" s="14" t="n"/>
       <c r="B470" s="23" t="str">
-        <f>IF(A470="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A470,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A470="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A470,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C470" s="5" t="n"/>
@@ -18537,7 +18537,7 @@
     <row r="471">
       <c r="A471" s="14" t="n"/>
       <c r="B471" s="23" t="str">
-        <f>IF(A471="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A471,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A471="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A471,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C471" s="5" t="n"/>
@@ -18554,7 +18554,7 @@
     <row r="472">
       <c r="A472" s="14" t="n"/>
       <c r="B472" s="23" t="str">
-        <f>IF(A472="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A472,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A472="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A472,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C472" s="5" t="n"/>
@@ -18571,7 +18571,7 @@
     <row r="473">
       <c r="A473" s="14" t="n"/>
       <c r="B473" s="23" t="str">
-        <f>IF(A473="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A473,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A473="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A473,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C473" s="5" t="n"/>
@@ -18588,7 +18588,7 @@
     <row r="474">
       <c r="A474" s="14" t="n"/>
       <c r="B474" s="23" t="str">
-        <f>IF(A474="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A474,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A474="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A474,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C474" s="5" t="n"/>
@@ -18605,7 +18605,7 @@
     <row r="475">
       <c r="A475" s="14" t="n"/>
       <c r="B475" s="23" t="str">
-        <f>IF(A475="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A475,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A475="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A475,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C475" s="5" t="n"/>
@@ -18622,7 +18622,7 @@
     <row r="476">
       <c r="A476" s="14" t="n"/>
       <c r="B476" s="23" t="str">
-        <f>IF(A476="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A476,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A476="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A476,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C476" s="5" t="n"/>
@@ -18639,7 +18639,7 @@
     <row r="477">
       <c r="A477" s="14" t="n"/>
       <c r="B477" s="23" t="str">
-        <f>IF(A477="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A477,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A477="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A477,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C477" s="5" t="n"/>
@@ -18656,7 +18656,7 @@
     <row r="478">
       <c r="A478" s="14" t="n"/>
       <c r="B478" s="23" t="str">
-        <f>IF(A478="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A478,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A478="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A478,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C478" s="5" t="n"/>
@@ -18673,7 +18673,7 @@
     <row r="479">
       <c r="A479" s="14" t="n"/>
       <c r="B479" s="23" t="str">
-        <f>IF(A479="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A479,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A479="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A479,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C479" s="5" t="n"/>
@@ -18690,7 +18690,7 @@
     <row r="480">
       <c r="A480" s="14" t="n"/>
       <c r="B480" s="23" t="str">
-        <f>IF(A480="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A480,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A480="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A480,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C480" s="5" t="n"/>
@@ -18707,7 +18707,7 @@
     <row r="481">
       <c r="A481" s="14" t="n"/>
       <c r="B481" s="23" t="str">
-        <f>IF(A481="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A481,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A481="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A481,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C481" s="5" t="n"/>
@@ -18724,7 +18724,7 @@
     <row r="482">
       <c r="A482" s="14" t="n"/>
       <c r="B482" s="23" t="str">
-        <f>IF(A482="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A482,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A482="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A482,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C482" s="5" t="n"/>
@@ -18741,7 +18741,7 @@
     <row r="483">
       <c r="A483" s="14" t="n"/>
       <c r="B483" s="23" t="str">
-        <f>IF(A483="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A483,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A483="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A483,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C483" s="5" t="n"/>
@@ -18758,7 +18758,7 @@
     <row r="484">
       <c r="A484" s="14" t="n"/>
       <c r="B484" s="23" t="str">
-        <f>IF(A484="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A484,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A484="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A484,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C484" s="5" t="n"/>
@@ -18775,7 +18775,7 @@
     <row r="485">
       <c r="A485" s="14" t="n"/>
       <c r="B485" s="23" t="str">
-        <f>IF(A485="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A485,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A485="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A485,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C485" s="5" t="n"/>
@@ -18792,7 +18792,7 @@
     <row r="486">
       <c r="A486" s="14" t="n"/>
       <c r="B486" s="23" t="str">
-        <f>IF(A486="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A486,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A486="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A486,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C486" s="5" t="n"/>
@@ -18809,7 +18809,7 @@
     <row r="487">
       <c r="A487" s="14" t="n"/>
       <c r="B487" s="23" t="str">
-        <f>IF(A487="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A487,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A487="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A487,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C487" s="5" t="n"/>
@@ -18826,7 +18826,7 @@
     <row r="488">
       <c r="A488" s="14" t="n"/>
       <c r="B488" s="23" t="str">
-        <f>IF(A488="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A488,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A488="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A488,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C488" s="5" t="n"/>
@@ -18843,7 +18843,7 @@
     <row r="489">
       <c r="A489" s="14" t="n"/>
       <c r="B489" s="23" t="str">
-        <f>IF(A489="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A489,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A489="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A489,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C489" s="5" t="n"/>
@@ -18860,7 +18860,7 @@
     <row r="490">
       <c r="A490" s="14" t="n"/>
       <c r="B490" s="23" t="str">
-        <f>IF(A490="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A490,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A490="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A490,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C490" s="5" t="n"/>
@@ -18877,7 +18877,7 @@
     <row r="491">
       <c r="A491" s="14" t="n"/>
       <c r="B491" s="23" t="str">
-        <f>IF(A491="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A491,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A491="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A491,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C491" s="5" t="n"/>
@@ -18894,7 +18894,7 @@
     <row r="492">
       <c r="A492" s="14" t="n"/>
       <c r="B492" s="23" t="str">
-        <f>IF(A492="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A492,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A492="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A492,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C492" s="5" t="n"/>
@@ -18911,7 +18911,7 @@
     <row r="493">
       <c r="A493" s="14" t="n"/>
       <c r="B493" s="23" t="str">
-        <f>IF(A493="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A493,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A493="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A493,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C493" s="5" t="n"/>
@@ -18928,7 +18928,7 @@
     <row r="494">
       <c r="A494" s="14" t="n"/>
       <c r="B494" s="23" t="str">
-        <f>IF(A494="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A494,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A494="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A494,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C494" s="5" t="n"/>
@@ -18945,7 +18945,7 @@
     <row r="495">
       <c r="A495" s="14" t="n"/>
       <c r="B495" s="23" t="str">
-        <f>IF(A495="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A495,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A495="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A495,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C495" s="5" t="n"/>
@@ -18962,7 +18962,7 @@
     <row r="496">
       <c r="A496" s="14" t="n"/>
       <c r="B496" s="23" t="str">
-        <f>IF(A496="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A496,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A496="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A496,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C496" s="5" t="n"/>
@@ -18979,7 +18979,7 @@
     <row r="497">
       <c r="A497" s="14" t="n"/>
       <c r="B497" s="23" t="str">
-        <f>IF(A497="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A497,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A497="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A497,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C497" s="5" t="n"/>
@@ -18996,7 +18996,7 @@
     <row r="498">
       <c r="A498" s="14" t="n"/>
       <c r="B498" s="23" t="str">
-        <f>IF(A498="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A498,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A498="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A498,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C498" s="5" t="n"/>
@@ -19013,7 +19013,7 @@
     <row r="499">
       <c r="A499" s="14" t="n"/>
       <c r="B499" s="23" t="str">
-        <f>IF(A499="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A499,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A499="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A499,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C499" s="5" t="n"/>
@@ -19030,7 +19030,7 @@
     <row r="500">
       <c r="A500" s="14" t="n"/>
       <c r="B500" s="23" t="str">
-        <f>IF(A500="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A500,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A500="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A500,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C500" s="5" t="n"/>
@@ -19047,7 +19047,7 @@
     <row r="501">
       <c r="A501" s="14" t="n"/>
       <c r="B501" s="23" t="str">
-        <f>IF(A501="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A501,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A501="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A501,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C501" s="5" t="n"/>
@@ -19064,7 +19064,7 @@
     <row r="502">
       <c r="A502" s="14" t="n"/>
       <c r="B502" s="23" t="str">
-        <f>IF(A502="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A502,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A502="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A502,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C502" s="5" t="n"/>
@@ -19081,7 +19081,7 @@
     <row r="503">
       <c r="A503" s="14" t="n"/>
       <c r="B503" s="23" t="str">
-        <f>IF(A503="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A503,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A503="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A503,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C503" s="5" t="n"/>
@@ -19098,7 +19098,7 @@
     <row r="504">
       <c r="A504" s="14" t="n"/>
       <c r="B504" s="23" t="str">
-        <f>IF(A504="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A504,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A504="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A504,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C504" s="5" t="n"/>
@@ -19115,7 +19115,7 @@
     <row r="505">
       <c r="A505" s="14" t="n"/>
       <c r="B505" s="23" t="str">
-        <f>IF(A505="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A505,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A505="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A505,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C505" s="5" t="n"/>
@@ -19132,7 +19132,7 @@
     <row r="506">
       <c r="A506" s="14" t="n"/>
       <c r="B506" s="23" t="str">
-        <f>IF(A506="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A506,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A506="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A506,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C506" s="5" t="n"/>
@@ -19149,7 +19149,7 @@
     <row r="507">
       <c r="A507" s="14" t="n"/>
       <c r="B507" s="23" t="str">
-        <f>IF(A507="","",IFERROR(INDEX('דירות ומכירות'!$I$14:$I$313,MATCH(A507,'דירות ומכירות'!$C$14:$C$313,0))&amp;"",""))</f>
+        <f>IF(A507="","",IFERROR(INDEX('דירות ומכירות'!$I$12:$I$311,MATCH(A507,'דירות ומכירות'!$C$12:$C$311,0))&amp;"",""))</f>
         <v/>
       </c>
       <c r="C507" s="5" t="n"/>
